--- a/development/one_file_rosetta_output/CPCT02070053T_rosetta.xlsx
+++ b/development/one_file_rosetta_output/CPCT02070053T_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E596"/>
+  <dimension ref="A1:F596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -482,7 +491,10 @@
       <c r="D3" s="4">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="4">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -536,9 +548,12 @@
         </is>
       </c>
       <c r="D4" s="4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -594,7 +609,10 @@
       <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -672,7 +690,10 @@
       <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -771,9 +792,12 @@
         </is>
       </c>
       <c r="D7" s="4">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -829,7 +853,10 @@
       <c r="D8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -857,7 +884,10 @@
       <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -885,7 +915,10 @@
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -963,7 +996,10 @@
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -991,7 +1027,10 @@
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1017,9 +1056,12 @@
         </is>
       </c>
       <c r="D13" s="4">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1073,9 +1115,12 @@
         </is>
       </c>
       <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1138,7 +1183,10 @@
       <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1207,9 +1255,12 @@
         </is>
       </c>
       <c r="D16" s="4">
+        <v>2</v>
+      </c>
+      <c r="E16" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1280,7 +1331,10 @@
       <c r="D17" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="4">
+        <v>1</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1356,9 +1410,12 @@
         </is>
       </c>
       <c r="D18" s="4">
+        <v>2</v>
+      </c>
+      <c r="E18" s="4">
         <v>1</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1444,7 +1501,10 @@
       <c r="D19" s="4">
         <v>2</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="4">
+        <v>2</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1530,7 +1590,10 @@
       <c r="D20" s="4">
         <v>1</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="4">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1556,9 +1619,12 @@
         </is>
       </c>
       <c r="D21" s="4">
+        <v>78</v>
+      </c>
+      <c r="E21" s="4">
         <v>1</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1612,9 +1678,12 @@
         </is>
       </c>
       <c r="D22" s="4">
+        <v>78</v>
+      </c>
+      <c r="E22" s="4">
         <v>2</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1668,9 +1737,12 @@
         </is>
       </c>
       <c r="D23" s="4">
+        <v>78</v>
+      </c>
+      <c r="E23" s="4">
         <v>3</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1724,9 +1796,12 @@
         </is>
       </c>
       <c r="D24" s="4">
+        <v>78</v>
+      </c>
+      <c r="E24" s="4">
         <v>4</v>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1780,9 +1855,12 @@
         </is>
       </c>
       <c r="D25" s="4">
+        <v>78</v>
+      </c>
+      <c r="E25" s="4">
         <v>5</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1836,9 +1914,12 @@
         </is>
       </c>
       <c r="D26" s="4">
+        <v>43</v>
+      </c>
+      <c r="E26" s="4">
         <v>1</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1892,9 +1973,12 @@
         </is>
       </c>
       <c r="D27" s="4">
+        <v>43</v>
+      </c>
+      <c r="E27" s="4">
         <v>2</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1948,9 +2032,12 @@
         </is>
       </c>
       <c r="D28" s="4">
+        <v>43</v>
+      </c>
+      <c r="E28" s="4">
         <v>3</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2004,9 +2091,12 @@
         </is>
       </c>
       <c r="D29" s="4">
+        <v>43</v>
+      </c>
+      <c r="E29" s="4">
         <v>4</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2060,9 +2150,12 @@
         </is>
       </c>
       <c r="D30" s="4">
+        <v>43</v>
+      </c>
+      <c r="E30" s="4">
         <v>5</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2116,9 +2209,12 @@
         </is>
       </c>
       <c r="D31" s="4">
+        <v>10</v>
+      </c>
+      <c r="E31" s="4">
         <v>1</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2172,9 +2268,12 @@
         </is>
       </c>
       <c r="D32" s="4">
+        <v>10</v>
+      </c>
+      <c r="E32" s="4">
         <v>2</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2228,9 +2327,12 @@
         </is>
       </c>
       <c r="D33" s="4">
+        <v>10</v>
+      </c>
+      <c r="E33" s="4">
         <v>3</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2284,9 +2386,12 @@
         </is>
       </c>
       <c r="D34" s="4">
+        <v>10</v>
+      </c>
+      <c r="E34" s="4">
         <v>4</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2340,9 +2445,12 @@
         </is>
       </c>
       <c r="D35" s="4">
+        <v>10</v>
+      </c>
+      <c r="E35" s="4">
         <v>5</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2396,9 +2504,12 @@
         </is>
       </c>
       <c r="D36" s="4">
+        <v>130</v>
+      </c>
+      <c r="E36" s="4">
         <v>1</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2459,9 +2570,12 @@
         </is>
       </c>
       <c r="D37" s="4">
+        <v>130</v>
+      </c>
+      <c r="E37" s="4">
         <v>2</v>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2522,9 +2636,12 @@
         </is>
       </c>
       <c r="D38" s="4">
+        <v>130</v>
+      </c>
+      <c r="E38" s="4">
         <v>3</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2585,9 +2702,12 @@
         </is>
       </c>
       <c r="D39" s="4">
+        <v>130</v>
+      </c>
+      <c r="E39" s="4">
         <v>4</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2648,9 +2768,12 @@
         </is>
       </c>
       <c r="D40" s="4">
+        <v>130</v>
+      </c>
+      <c r="E40" s="4">
         <v>5</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2711,9 +2834,12 @@
         </is>
       </c>
       <c r="D41" s="4">
+        <v>48</v>
+      </c>
+      <c r="E41" s="4">
         <v>1</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2774,9 +2900,12 @@
         </is>
       </c>
       <c r="D42" s="4">
+        <v>48</v>
+      </c>
+      <c r="E42" s="4">
         <v>2</v>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2837,9 +2966,12 @@
         </is>
       </c>
       <c r="D43" s="4">
+        <v>48</v>
+      </c>
+      <c r="E43" s="4">
         <v>3</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2900,9 +3032,12 @@
         </is>
       </c>
       <c r="D44" s="4">
+        <v>48</v>
+      </c>
+      <c r="E44" s="4">
         <v>4</v>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2963,9 +3098,12 @@
         </is>
       </c>
       <c r="D45" s="4">
+        <v>48</v>
+      </c>
+      <c r="E45" s="4">
         <v>5</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3026,9 +3164,12 @@
         </is>
       </c>
       <c r="D46" s="4">
+        <v>41</v>
+      </c>
+      <c r="E46" s="4">
         <v>1</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3089,9 +3230,12 @@
         </is>
       </c>
       <c r="D47" s="4">
+        <v>41</v>
+      </c>
+      <c r="E47" s="4">
         <v>2</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3152,9 +3296,12 @@
         </is>
       </c>
       <c r="D48" s="4">
+        <v>41</v>
+      </c>
+      <c r="E48" s="4">
         <v>3</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3215,9 +3362,12 @@
         </is>
       </c>
       <c r="D49" s="4">
+        <v>41</v>
+      </c>
+      <c r="E49" s="4">
         <v>4</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3278,9 +3428,12 @@
         </is>
       </c>
       <c r="D50" s="4">
+        <v>41</v>
+      </c>
+      <c r="E50" s="4">
         <v>5</v>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3341,9 +3494,12 @@
         </is>
       </c>
       <c r="D51" s="4">
+        <v>70</v>
+      </c>
+      <c r="E51" s="4">
         <v>1</v>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3412,9 +3568,12 @@
         </is>
       </c>
       <c r="D52" s="4">
+        <v>70</v>
+      </c>
+      <c r="E52" s="4">
         <v>2</v>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3483,9 +3642,12 @@
         </is>
       </c>
       <c r="D53" s="4">
+        <v>70</v>
+      </c>
+      <c r="E53" s="4">
         <v>3</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3554,9 +3716,12 @@
         </is>
       </c>
       <c r="D54" s="4">
+        <v>70</v>
+      </c>
+      <c r="E54" s="4">
         <v>4</v>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3625,9 +3790,12 @@
         </is>
       </c>
       <c r="D55" s="4">
+        <v>70</v>
+      </c>
+      <c r="E55" s="4">
         <v>5</v>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3696,9 +3864,12 @@
         </is>
       </c>
       <c r="D56" s="4">
+        <v>61</v>
+      </c>
+      <c r="E56" s="4">
         <v>1</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3767,9 +3938,12 @@
         </is>
       </c>
       <c r="D57" s="4">
+        <v>61</v>
+      </c>
+      <c r="E57" s="4">
         <v>2</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3838,9 +4012,12 @@
         </is>
       </c>
       <c r="D58" s="4">
+        <v>61</v>
+      </c>
+      <c r="E58" s="4">
         <v>3</v>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3909,9 +4086,12 @@
         </is>
       </c>
       <c r="D59" s="4">
+        <v>61</v>
+      </c>
+      <c r="E59" s="4">
         <v>4</v>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3980,9 +4160,12 @@
         </is>
       </c>
       <c r="D60" s="4">
+        <v>61</v>
+      </c>
+      <c r="E60" s="4">
         <v>5</v>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4051,9 +4234,12 @@
         </is>
       </c>
       <c r="D61" s="4">
+        <v>37</v>
+      </c>
+      <c r="E61" s="4">
         <v>1</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4122,9 +4308,12 @@
         </is>
       </c>
       <c r="D62" s="4">
+        <v>37</v>
+      </c>
+      <c r="E62" s="4">
         <v>2</v>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4193,9 +4382,12 @@
         </is>
       </c>
       <c r="D63" s="4">
+        <v>37</v>
+      </c>
+      <c r="E63" s="4">
         <v>3</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4264,9 +4456,12 @@
         </is>
       </c>
       <c r="D64" s="4">
+        <v>37</v>
+      </c>
+      <c r="E64" s="4">
         <v>4</v>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4335,9 +4530,12 @@
         </is>
       </c>
       <c r="D65" s="4">
+        <v>37</v>
+      </c>
+      <c r="E65" s="4">
         <v>5</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4406,9 +4604,12 @@
         </is>
       </c>
       <c r="D66" s="4">
+        <v>134</v>
+      </c>
+      <c r="E66" s="4">
         <v>1</v>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4484,9 +4685,12 @@
         </is>
       </c>
       <c r="D67" s="4">
+        <v>134</v>
+      </c>
+      <c r="E67" s="4">
         <v>2</v>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4562,9 +4766,12 @@
         </is>
       </c>
       <c r="D68" s="4">
+        <v>134</v>
+      </c>
+      <c r="E68" s="4">
         <v>3</v>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4640,9 +4847,12 @@
         </is>
       </c>
       <c r="D69" s="4">
+        <v>134</v>
+      </c>
+      <c r="E69" s="4">
         <v>4</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4718,9 +4928,12 @@
         </is>
       </c>
       <c r="D70" s="4">
+        <v>134</v>
+      </c>
+      <c r="E70" s="4">
         <v>5</v>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4796,9 +5009,12 @@
         </is>
       </c>
       <c r="D71" s="4">
+        <v>145</v>
+      </c>
+      <c r="E71" s="4">
         <v>1</v>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4874,9 +5090,12 @@
         </is>
       </c>
       <c r="D72" s="4">
+        <v>145</v>
+      </c>
+      <c r="E72" s="4">
         <v>2</v>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4952,9 +5171,12 @@
         </is>
       </c>
       <c r="D73" s="4">
+        <v>145</v>
+      </c>
+      <c r="E73" s="4">
         <v>3</v>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5030,9 +5252,12 @@
         </is>
       </c>
       <c r="D74" s="4">
+        <v>145</v>
+      </c>
+      <c r="E74" s="4">
         <v>4</v>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5108,9 +5333,12 @@
         </is>
       </c>
       <c r="D75" s="4">
+        <v>145</v>
+      </c>
+      <c r="E75" s="4">
         <v>5</v>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5186,9 +5414,12 @@
         </is>
       </c>
       <c r="D76" s="4">
+        <v>43</v>
+      </c>
+      <c r="E76" s="4">
         <v>1</v>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5264,9 +5495,12 @@
         </is>
       </c>
       <c r="D77" s="4">
+        <v>43</v>
+      </c>
+      <c r="E77" s="4">
         <v>2</v>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5342,9 +5576,12 @@
         </is>
       </c>
       <c r="D78" s="4">
+        <v>43</v>
+      </c>
+      <c r="E78" s="4">
         <v>3</v>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5420,9 +5657,12 @@
         </is>
       </c>
       <c r="D79" s="4">
+        <v>43</v>
+      </c>
+      <c r="E79" s="4">
         <v>4</v>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5498,9 +5738,12 @@
         </is>
       </c>
       <c r="D80" s="4">
+        <v>43</v>
+      </c>
+      <c r="E80" s="4">
         <v>5</v>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5576,9 +5819,12 @@
         </is>
       </c>
       <c r="D81" s="4">
+        <v>36</v>
+      </c>
+      <c r="E81" s="4">
         <v>1</v>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5662,9 +5908,12 @@
         </is>
       </c>
       <c r="D82" s="4">
+        <v>36</v>
+      </c>
+      <c r="E82" s="4">
         <v>2</v>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5748,9 +5997,12 @@
         </is>
       </c>
       <c r="D83" s="4">
+        <v>36</v>
+      </c>
+      <c r="E83" s="4">
         <v>3</v>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5834,9 +6086,12 @@
         </is>
       </c>
       <c r="D84" s="4">
+        <v>36</v>
+      </c>
+      <c r="E84" s="4">
         <v>4</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5920,9 +6175,12 @@
         </is>
       </c>
       <c r="D85" s="4">
+        <v>36</v>
+      </c>
+      <c r="E85" s="4">
         <v>5</v>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6006,9 +6264,12 @@
         </is>
       </c>
       <c r="D86" s="4">
+        <v>24</v>
+      </c>
+      <c r="E86" s="4">
         <v>1</v>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6092,9 +6353,12 @@
         </is>
       </c>
       <c r="D87" s="4">
+        <v>24</v>
+      </c>
+      <c r="E87" s="4">
         <v>2</v>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6178,9 +6442,12 @@
         </is>
       </c>
       <c r="D88" s="4">
+        <v>24</v>
+      </c>
+      <c r="E88" s="4">
         <v>3</v>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6264,9 +6531,12 @@
         </is>
       </c>
       <c r="D89" s="4">
+        <v>24</v>
+      </c>
+      <c r="E89" s="4">
         <v>4</v>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6350,9 +6620,12 @@
         </is>
       </c>
       <c r="D90" s="4">
+        <v>24</v>
+      </c>
+      <c r="E90" s="4">
         <v>5</v>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6436,9 +6709,12 @@
         </is>
       </c>
       <c r="D91" s="4">
+        <v>40</v>
+      </c>
+      <c r="E91" s="4">
         <v>1</v>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6522,9 +6798,12 @@
         </is>
       </c>
       <c r="D92" s="4">
+        <v>40</v>
+      </c>
+      <c r="E92" s="4">
         <v>2</v>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6608,9 +6887,12 @@
         </is>
       </c>
       <c r="D93" s="4">
+        <v>40</v>
+      </c>
+      <c r="E93" s="4">
         <v>3</v>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6694,9 +6976,12 @@
         </is>
       </c>
       <c r="D94" s="4">
+        <v>40</v>
+      </c>
+      <c r="E94" s="4">
         <v>4</v>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6780,9 +7065,12 @@
         </is>
       </c>
       <c r="D95" s="4">
+        <v>40</v>
+      </c>
+      <c r="E95" s="4">
         <v>5</v>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6866,9 +7154,12 @@
         </is>
       </c>
       <c r="D96" s="4">
+        <v>19</v>
+      </c>
+      <c r="E96" s="4">
         <v>1</v>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6959,9 +7250,12 @@
         </is>
       </c>
       <c r="D97" s="4">
+        <v>19</v>
+      </c>
+      <c r="E97" s="4">
         <v>2</v>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7052,9 +7346,12 @@
         </is>
       </c>
       <c r="D98" s="4">
+        <v>19</v>
+      </c>
+      <c r="E98" s="4">
         <v>3</v>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7145,9 +7442,12 @@
         </is>
       </c>
       <c r="D99" s="4">
+        <v>19</v>
+      </c>
+      <c r="E99" s="4">
         <v>4</v>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7238,9 +7538,12 @@
         </is>
       </c>
       <c r="D100" s="4">
+        <v>19</v>
+      </c>
+      <c r="E100" s="4">
         <v>5</v>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7331,9 +7634,12 @@
         </is>
       </c>
       <c r="D101" s="4">
+        <v>18</v>
+      </c>
+      <c r="E101" s="4">
         <v>1</v>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7424,9 +7730,12 @@
         </is>
       </c>
       <c r="D102" s="4">
+        <v>18</v>
+      </c>
+      <c r="E102" s="4">
         <v>2</v>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7517,9 +7826,12 @@
         </is>
       </c>
       <c r="D103" s="4">
+        <v>18</v>
+      </c>
+      <c r="E103" s="4">
         <v>3</v>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7610,9 +7922,12 @@
         </is>
       </c>
       <c r="D104" s="4">
+        <v>18</v>
+      </c>
+      <c r="E104" s="4">
         <v>4</v>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7703,9 +8018,12 @@
         </is>
       </c>
       <c r="D105" s="4">
+        <v>18</v>
+      </c>
+      <c r="E105" s="4">
         <v>5</v>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7796,9 +8114,12 @@
         </is>
       </c>
       <c r="D106" s="4">
+        <v>13</v>
+      </c>
+      <c r="E106" s="4">
         <v>1</v>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7889,9 +8210,12 @@
         </is>
       </c>
       <c r="D107" s="4">
+        <v>13</v>
+      </c>
+      <c r="E107" s="4">
         <v>2</v>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7982,9 +8306,12 @@
         </is>
       </c>
       <c r="D108" s="4">
+        <v>13</v>
+      </c>
+      <c r="E108" s="4">
         <v>3</v>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8075,9 +8402,12 @@
         </is>
       </c>
       <c r="D109" s="4">
+        <v>13</v>
+      </c>
+      <c r="E109" s="4">
         <v>4</v>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8168,9 +8498,12 @@
         </is>
       </c>
       <c r="D110" s="4">
+        <v>13</v>
+      </c>
+      <c r="E110" s="4">
         <v>5</v>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8261,9 +8594,12 @@
         </is>
       </c>
       <c r="D111" s="4">
+        <v>9</v>
+      </c>
+      <c r="E111" s="4">
         <v>1</v>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8362,9 +8698,12 @@
         </is>
       </c>
       <c r="D112" s="4">
+        <v>9</v>
+      </c>
+      <c r="E112" s="4">
         <v>2</v>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8463,9 +8802,12 @@
         </is>
       </c>
       <c r="D113" s="4">
+        <v>9</v>
+      </c>
+      <c r="E113" s="4">
         <v>3</v>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8564,9 +8906,12 @@
         </is>
       </c>
       <c r="D114" s="4">
+        <v>9</v>
+      </c>
+      <c r="E114" s="4">
         <v>1</v>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8665,9 +9010,12 @@
         </is>
       </c>
       <c r="D115" s="4">
+        <v>9</v>
+      </c>
+      <c r="E115" s="4">
         <v>2</v>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8766,9 +9114,12 @@
         </is>
       </c>
       <c r="D116" s="4">
+        <v>9</v>
+      </c>
+      <c r="E116" s="4">
         <v>3</v>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8867,9 +9218,12 @@
         </is>
       </c>
       <c r="D117" s="4">
+        <v>9</v>
+      </c>
+      <c r="E117" s="4">
         <v>4</v>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8968,9 +9322,12 @@
         </is>
       </c>
       <c r="D118" s="4">
+        <v>9</v>
+      </c>
+      <c r="E118" s="4">
         <v>5</v>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9069,9 +9426,12 @@
         </is>
       </c>
       <c r="D119" s="4">
+        <v>10</v>
+      </c>
+      <c r="E119" s="4">
         <v>1</v>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9170,9 +9530,12 @@
         </is>
       </c>
       <c r="D120" s="4">
+        <v>10</v>
+      </c>
+      <c r="E120" s="4">
         <v>2</v>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9271,9 +9634,12 @@
         </is>
       </c>
       <c r="D121" s="4">
+        <v>10</v>
+      </c>
+      <c r="E121" s="4">
         <v>3</v>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9372,9 +9738,12 @@
         </is>
       </c>
       <c r="D122" s="4">
+        <v>10</v>
+      </c>
+      <c r="E122" s="4">
         <v>4</v>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9473,9 +9842,12 @@
         </is>
       </c>
       <c r="D123" s="4">
+        <v>10</v>
+      </c>
+      <c r="E123" s="4">
         <v>5</v>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9574,9 +9946,12 @@
         </is>
       </c>
       <c r="D124" s="4">
+        <v>2</v>
+      </c>
+      <c r="E124" s="4">
         <v>1</v>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9684,7 +10059,10 @@
       <c r="D125" s="4">
         <v>1</v>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E125" s="4">
+        <v>1</v>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9790,9 +10168,12 @@
         </is>
       </c>
       <c r="D126" s="4">
+        <v>3</v>
+      </c>
+      <c r="E126" s="4">
         <v>1</v>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9818,9 +10199,12 @@
         </is>
       </c>
       <c r="D127" s="4">
+        <v>4</v>
+      </c>
+      <c r="E127" s="4">
         <v>1</v>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9934,9 +10318,12 @@
         </is>
       </c>
       <c r="D128" s="4">
+        <v>4</v>
+      </c>
+      <c r="E128" s="4">
         <v>2</v>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10050,9 +10437,12 @@
         </is>
       </c>
       <c r="D129" s="4">
+        <v>7</v>
+      </c>
+      <c r="E129" s="4">
         <v>1</v>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10168,7 +10558,10 @@
       <c r="D130" s="4">
         <v>1</v>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="E130" s="4">
+        <v>1</v>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10282,9 +10675,12 @@
         </is>
       </c>
       <c r="D131" s="4">
+        <v>2</v>
+      </c>
+      <c r="E131" s="4">
         <v>1</v>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10338,9 +10734,12 @@
         </is>
       </c>
       <c r="D132" s="4">
+        <v>2</v>
+      </c>
+      <c r="E132" s="4">
         <v>1</v>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10366,9 +10765,12 @@
         </is>
       </c>
       <c r="D133" s="4">
+        <v>2</v>
+      </c>
+      <c r="E133" s="4">
         <v>1</v>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10394,9 +10796,12 @@
         </is>
       </c>
       <c r="D134" s="4">
+        <v>3</v>
+      </c>
+      <c r="E134" s="4">
         <v>1</v>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10457,9 +10862,12 @@
         </is>
       </c>
       <c r="D135" s="4">
+        <v>3</v>
+      </c>
+      <c r="E135" s="4">
         <v>1</v>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10528,9 +10936,12 @@
         </is>
       </c>
       <c r="D136" s="4">
+        <v>2</v>
+      </c>
+      <c r="E136" s="4">
         <v>1</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10601,7 +11012,10 @@
       <c r="D137" s="4">
         <v>1</v>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="E137" s="4">
+        <v>1</v>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10629,7 +11043,10 @@
       <c r="D138" s="4">
         <v>1</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="E138" s="4">
+        <v>1</v>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10705,9 +11122,12 @@
         </is>
       </c>
       <c r="D139" s="4">
+        <v>2</v>
+      </c>
+      <c r="E139" s="4">
         <v>1</v>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10785,7 +11205,10 @@
       <c r="D140" s="4">
         <v>2</v>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="E140" s="4">
+        <v>2</v>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10863,7 +11286,10 @@
       <c r="D141" s="4">
         <v>1</v>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="E141" s="4">
+        <v>1</v>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10949,7 +11375,10 @@
       <c r="D142" s="4">
         <v>1</v>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="E142" s="4">
+        <v>1</v>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10977,7 +11406,10 @@
       <c r="D143" s="4">
         <v>1</v>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="E143" s="4">
+        <v>1</v>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11070,7 +11502,10 @@
       <c r="D144" s="4">
         <v>1</v>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E144" s="4">
+        <v>1</v>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11163,7 +11598,10 @@
       <c r="D145" s="4">
         <v>1</v>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="E145" s="4">
+        <v>1</v>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11264,7 +11702,10 @@
       <c r="D146" s="4">
         <v>1</v>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E146" s="4">
+        <v>1</v>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11292,7 +11733,10 @@
       <c r="D147" s="4">
         <v>1</v>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E147" s="4">
+        <v>1</v>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11400,7 +11844,10 @@
       <c r="D148" s="4">
         <v>1</v>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E148" s="4">
+        <v>1</v>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11514,9 +11961,12 @@
         </is>
       </c>
       <c r="D149" s="4">
+        <v>2</v>
+      </c>
+      <c r="E149" s="4">
         <v>1</v>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11572,7 +12022,10 @@
       <c r="D150" s="4">
         <v>2</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="E150" s="4">
+        <v>2</v>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11626,9 +12079,12 @@
         </is>
       </c>
       <c r="D151" s="4">
+        <v>6</v>
+      </c>
+      <c r="E151" s="4">
         <v>1</v>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11689,9 +12145,12 @@
         </is>
       </c>
       <c r="D152" s="4">
+        <v>6</v>
+      </c>
+      <c r="E152" s="4">
         <v>2</v>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11752,9 +12211,12 @@
         </is>
       </c>
       <c r="D153" s="4">
+        <v>6</v>
+      </c>
+      <c r="E153" s="4">
         <v>3</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11817,7 +12279,10 @@
       <c r="D154" s="4">
         <v>1</v>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="E154" s="4">
+        <v>1</v>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11843,9 +12308,12 @@
         </is>
       </c>
       <c r="D155" s="4">
+        <v>2</v>
+      </c>
+      <c r="E155" s="4">
         <v>1</v>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11906,9 +12374,12 @@
         </is>
       </c>
       <c r="D156" s="4">
+        <v>3</v>
+      </c>
+      <c r="E156" s="4">
         <v>1</v>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11977,9 +12448,12 @@
         </is>
       </c>
       <c r="D157" s="4">
+        <v>4</v>
+      </c>
+      <c r="E157" s="4">
         <v>1</v>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12048,9 +12522,12 @@
         </is>
       </c>
       <c r="D158" s="4">
+        <v>4</v>
+      </c>
+      <c r="E158" s="4">
         <v>2</v>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12121,7 +12598,10 @@
       <c r="D159" s="4">
         <v>1</v>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="E159" s="4">
+        <v>1</v>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12197,9 +12677,12 @@
         </is>
       </c>
       <c r="D160" s="4">
+        <v>2</v>
+      </c>
+      <c r="E160" s="4">
         <v>1</v>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12227,7 +12710,10 @@
       <c r="D161" s="4">
         <v>1</v>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="E161" s="4">
+        <v>1</v>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12255,7 +12741,10 @@
       <c r="D162" s="4">
         <v>1</v>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="E162" s="4">
+        <v>1</v>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12283,7 +12772,10 @@
       <c r="D163" s="4">
         <v>1</v>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="E163" s="4">
+        <v>1</v>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12376,7 +12868,10 @@
       <c r="D164" s="4">
         <v>1</v>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="E164" s="4">
+        <v>1</v>
+      </c>
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12477,7 +12972,10 @@
       <c r="D165" s="4">
         <v>1</v>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="E165" s="4">
+        <v>1</v>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12505,7 +13003,10 @@
       <c r="D166" s="4">
         <v>1</v>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="E166" s="4">
+        <v>1</v>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12533,7 +13034,10 @@
       <c r="D167" s="4">
         <v>1</v>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="E167" s="4">
+        <v>1</v>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12647,9 +13151,12 @@
         </is>
       </c>
       <c r="D168" s="4">
+        <v>3</v>
+      </c>
+      <c r="E168" s="4">
         <v>1</v>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12703,9 +13210,12 @@
         </is>
       </c>
       <c r="D169" s="4">
+        <v>3</v>
+      </c>
+      <c r="E169" s="4">
         <v>2</v>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12759,9 +13269,12 @@
         </is>
       </c>
       <c r="D170" s="4">
+        <v>3</v>
+      </c>
+      <c r="E170" s="4">
         <v>1</v>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12815,9 +13328,12 @@
         </is>
       </c>
       <c r="D171" s="4">
+        <v>3</v>
+      </c>
+      <c r="E171" s="4">
         <v>2</v>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12873,7 +13389,10 @@
       <c r="D172" s="4">
         <v>3</v>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="E172" s="4">
+        <v>3</v>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12929,7 +13448,10 @@
       <c r="D173" s="4">
         <v>1</v>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="E173" s="4">
+        <v>1</v>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12957,7 +13479,10 @@
       <c r="D174" s="4">
         <v>1</v>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="E174" s="4">
+        <v>1</v>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13050,7 +13575,10 @@
       <c r="D175" s="4">
         <v>1</v>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="E175" s="4">
+        <v>1</v>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -13076,9 +13604,12 @@
         </is>
       </c>
       <c r="D176" s="4">
+        <v>3</v>
+      </c>
+      <c r="E176" s="4">
         <v>1</v>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13134,7 +13665,10 @@
       <c r="D177" s="4">
         <v>1</v>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="E177" s="4">
+        <v>1</v>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13195,9 +13729,12 @@
         </is>
       </c>
       <c r="D178" s="4">
+        <v>2</v>
+      </c>
+      <c r="E178" s="4">
         <v>1</v>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13268,7 +13805,10 @@
       <c r="D179" s="4">
         <v>1</v>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="E179" s="4">
+        <v>1</v>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13339,7 +13879,10 @@
       <c r="D180" s="4">
         <v>1</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="E180" s="4">
+        <v>1</v>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -13367,7 +13910,10 @@
       <c r="D181" s="4">
         <v>1</v>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="E181" s="4">
+        <v>1</v>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13475,7 +14021,10 @@
       <c r="D182" s="4">
         <v>1</v>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="E182" s="4">
+        <v>1</v>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -13503,7 +14052,10 @@
       <c r="D183" s="4">
         <v>1</v>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="E183" s="4">
+        <v>1</v>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13626,7 +14178,10 @@
       <c r="D184" s="4">
         <v>1</v>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="E184" s="4">
+        <v>1</v>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13680,9 +14235,12 @@
         </is>
       </c>
       <c r="D185" s="4">
+        <v>4</v>
+      </c>
+      <c r="E185" s="4">
         <v>1</v>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13743,9 +14301,12 @@
         </is>
       </c>
       <c r="D186" s="4">
+        <v>4</v>
+      </c>
+      <c r="E186" s="4">
         <v>2</v>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13806,9 +14367,12 @@
         </is>
       </c>
       <c r="D187" s="4">
+        <v>2</v>
+      </c>
+      <c r="E187" s="4">
         <v>1</v>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13884,9 +14448,12 @@
         </is>
       </c>
       <c r="D188" s="4">
+        <v>2</v>
+      </c>
+      <c r="E188" s="4">
         <v>1</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13972,7 +14539,10 @@
       <c r="D189" s="4">
         <v>2</v>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="4">
+        <v>2</v>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14056,9 +14626,12 @@
         </is>
       </c>
       <c r="D190" s="4">
+        <v>2</v>
+      </c>
+      <c r="E190" s="4">
         <v>1</v>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14086,7 +14659,10 @@
       <c r="D191" s="4">
         <v>1</v>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="E191" s="4">
+        <v>1</v>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14112,9 +14688,12 @@
         </is>
       </c>
       <c r="D192" s="4">
+        <v>4</v>
+      </c>
+      <c r="E192" s="4">
         <v>1</v>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14213,9 +14792,12 @@
         </is>
       </c>
       <c r="D193" s="4">
+        <v>4</v>
+      </c>
+      <c r="E193" s="4">
         <v>2</v>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14314,9 +14896,12 @@
         </is>
       </c>
       <c r="D194" s="4">
+        <v>4</v>
+      </c>
+      <c r="E194" s="4">
         <v>3</v>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14415,9 +15000,12 @@
         </is>
       </c>
       <c r="D195" s="4">
+        <v>8</v>
+      </c>
+      <c r="E195" s="4">
         <v>1</v>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14516,9 +15104,12 @@
         </is>
       </c>
       <c r="D196" s="4">
+        <v>8</v>
+      </c>
+      <c r="E196" s="4">
         <v>2</v>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="F196" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14617,9 +15208,12 @@
         </is>
       </c>
       <c r="D197" s="4">
+        <v>8</v>
+      </c>
+      <c r="E197" s="4">
         <v>3</v>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14718,9 +15312,12 @@
         </is>
       </c>
       <c r="D198" s="4">
+        <v>8</v>
+      </c>
+      <c r="E198" s="4">
         <v>4</v>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="F198" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14819,9 +15416,12 @@
         </is>
       </c>
       <c r="D199" s="4">
+        <v>8</v>
+      </c>
+      <c r="E199" s="4">
         <v>5</v>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="F199" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14920,9 +15520,12 @@
         </is>
       </c>
       <c r="D200" s="4">
+        <v>6</v>
+      </c>
+      <c r="E200" s="4">
         <v>1</v>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15023,7 +15626,10 @@
       <c r="D201" s="4">
         <v>1</v>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="E201" s="4">
+        <v>1</v>
+      </c>
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -15049,9 +15655,12 @@
         </is>
       </c>
       <c r="D202" s="4">
+        <v>5</v>
+      </c>
+      <c r="E202" s="4">
         <v>1</v>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15159,7 +15768,10 @@
       <c r="D203" s="4">
         <v>1</v>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="E203" s="4">
+        <v>1</v>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -15185,9 +15797,12 @@
         </is>
       </c>
       <c r="D204" s="4">
+        <v>6</v>
+      </c>
+      <c r="E204" s="4">
         <v>1</v>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15301,9 +15916,12 @@
         </is>
       </c>
       <c r="D205" s="4">
+        <v>6</v>
+      </c>
+      <c r="E205" s="4">
         <v>2</v>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15417,9 +16035,12 @@
         </is>
       </c>
       <c r="D206" s="4">
+        <v>3</v>
+      </c>
+      <c r="E206" s="4">
         <v>1</v>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15533,9 +16154,12 @@
         </is>
       </c>
       <c r="D207" s="4">
+        <v>3</v>
+      </c>
+      <c r="E207" s="4">
         <v>2</v>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15651,7 +16275,10 @@
       <c r="D208" s="4">
         <v>3</v>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="E208" s="4">
+        <v>3</v>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15765,9 +16392,12 @@
         </is>
       </c>
       <c r="D209" s="4">
+        <v>16</v>
+      </c>
+      <c r="E209" s="4">
         <v>1</v>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15881,9 +16511,12 @@
         </is>
       </c>
       <c r="D210" s="4">
+        <v>16</v>
+      </c>
+      <c r="E210" s="4">
         <v>2</v>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15997,9 +16630,12 @@
         </is>
       </c>
       <c r="D211" s="4">
+        <v>16</v>
+      </c>
+      <c r="E211" s="4">
         <v>3</v>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="F211" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16113,9 +16749,12 @@
         </is>
       </c>
       <c r="D212" s="4">
+        <v>16</v>
+      </c>
+      <c r="E212" s="4">
         <v>4</v>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16229,9 +16868,12 @@
         </is>
       </c>
       <c r="D213" s="4">
+        <v>16</v>
+      </c>
+      <c r="E213" s="4">
         <v>5</v>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16345,9 +16987,12 @@
         </is>
       </c>
       <c r="D214" s="4">
+        <v>10</v>
+      </c>
+      <c r="E214" s="4">
         <v>1</v>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16468,9 +17113,12 @@
         </is>
       </c>
       <c r="D215" s="4">
+        <v>10</v>
+      </c>
+      <c r="E215" s="4">
         <v>2</v>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16591,9 +17239,12 @@
         </is>
       </c>
       <c r="D216" s="4">
+        <v>10</v>
+      </c>
+      <c r="E216" s="4">
         <v>3</v>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16714,9 +17365,12 @@
         </is>
       </c>
       <c r="D217" s="4">
+        <v>10</v>
+      </c>
+      <c r="E217" s="4">
         <v>4</v>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16837,9 +17491,12 @@
         </is>
       </c>
       <c r="D218" s="4">
+        <v>10</v>
+      </c>
+      <c r="E218" s="4">
         <v>5</v>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="F218" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16960,9 +17617,12 @@
         </is>
       </c>
       <c r="D219" s="4">
+        <v>7</v>
+      </c>
+      <c r="E219" s="4">
         <v>1</v>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="F219" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17083,9 +17743,12 @@
         </is>
       </c>
       <c r="D220" s="4">
+        <v>7</v>
+      </c>
+      <c r="E220" s="4">
         <v>2</v>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17206,9 +17869,12 @@
         </is>
       </c>
       <c r="D221" s="4">
+        <v>7</v>
+      </c>
+      <c r="E221" s="4">
         <v>3</v>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17329,9 +17995,12 @@
         </is>
       </c>
       <c r="D222" s="4">
+        <v>8</v>
+      </c>
+      <c r="E222" s="4">
         <v>1</v>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="F222" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17452,9 +18121,12 @@
         </is>
       </c>
       <c r="D223" s="4">
+        <v>8</v>
+      </c>
+      <c r="E223" s="4">
         <v>2</v>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="F223" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17575,9 +18247,12 @@
         </is>
       </c>
       <c r="D224" s="4">
+        <v>8</v>
+      </c>
+      <c r="E224" s="4">
         <v>3</v>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="F224" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17698,9 +18373,12 @@
         </is>
       </c>
       <c r="D225" s="4">
+        <v>8</v>
+      </c>
+      <c r="E225" s="4">
         <v>4</v>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="F225" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17821,9 +18499,12 @@
         </is>
       </c>
       <c r="D226" s="4">
+        <v>8</v>
+      </c>
+      <c r="E226" s="4">
         <v>5</v>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="F226" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17946,7 +18627,10 @@
       <c r="D227" s="4">
         <v>1</v>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="E227" s="4">
+        <v>1</v>
+      </c>
+      <c r="F227" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -17974,7 +18658,10 @@
       <c r="D228" s="4">
         <v>1</v>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="E228" s="4">
+        <v>1</v>
+      </c>
+      <c r="F228" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -18002,7 +18689,10 @@
       <c r="D229" s="4">
         <v>1</v>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="E229" s="4">
+        <v>1</v>
+      </c>
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -18030,7 +18720,10 @@
       <c r="D230" s="4">
         <v>1</v>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="E230" s="4">
+        <v>1</v>
+      </c>
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -18056,9 +18749,12 @@
         </is>
       </c>
       <c r="D231" s="4">
+        <v>2</v>
+      </c>
+      <c r="E231" s="4">
         <v>1</v>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="F231" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18157,9 +18853,12 @@
         </is>
       </c>
       <c r="D232" s="4">
+        <v>4</v>
+      </c>
+      <c r="E232" s="4">
         <v>1</v>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="F232" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18265,9 +18964,12 @@
         </is>
       </c>
       <c r="D233" s="4">
+        <v>3</v>
+      </c>
+      <c r="E233" s="4">
         <v>1</v>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="F233" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18373,9 +19075,12 @@
         </is>
       </c>
       <c r="D234" s="4">
+        <v>3</v>
+      </c>
+      <c r="E234" s="4">
         <v>2</v>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="F234" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18481,9 +19186,12 @@
         </is>
       </c>
       <c r="D235" s="4">
+        <v>3</v>
+      </c>
+      <c r="E235" s="4">
         <v>1</v>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="F235" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -18509,9 +19217,12 @@
         </is>
       </c>
       <c r="D236" s="4">
+        <v>5</v>
+      </c>
+      <c r="E236" s="4">
         <v>1</v>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="F236" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18627,7 +19338,10 @@
       <c r="D237" s="4">
         <v>1</v>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="E237" s="4">
+        <v>1</v>
+      </c>
+      <c r="F237" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -18653,9 +19367,12 @@
         </is>
       </c>
       <c r="D238" s="4">
+        <v>6</v>
+      </c>
+      <c r="E238" s="4">
         <v>1</v>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="F238" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18769,9 +19486,12 @@
         </is>
       </c>
       <c r="D239" s="4">
+        <v>6</v>
+      </c>
+      <c r="E239" s="4">
         <v>2</v>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18885,9 +19605,12 @@
         </is>
       </c>
       <c r="D240" s="4">
+        <v>6</v>
+      </c>
+      <c r="E240" s="4">
         <v>3</v>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19001,9 +19724,12 @@
         </is>
       </c>
       <c r="D241" s="4">
+        <v>4</v>
+      </c>
+      <c r="E241" s="4">
         <v>1</v>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19124,9 +19850,12 @@
         </is>
       </c>
       <c r="D242" s="4">
+        <v>4</v>
+      </c>
+      <c r="E242" s="4">
         <v>2</v>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19247,9 +19976,12 @@
         </is>
       </c>
       <c r="D243" s="4">
+        <v>6</v>
+      </c>
+      <c r="E243" s="4">
         <v>1</v>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="F243" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19370,9 +20102,12 @@
         </is>
       </c>
       <c r="D244" s="4">
+        <v>6</v>
+      </c>
+      <c r="E244" s="4">
         <v>2</v>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19493,9 +20228,12 @@
         </is>
       </c>
       <c r="D245" s="4">
+        <v>3</v>
+      </c>
+      <c r="E245" s="4">
         <v>1</v>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="F245" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19616,9 +20354,12 @@
         </is>
       </c>
       <c r="D246" s="4">
+        <v>3</v>
+      </c>
+      <c r="E246" s="4">
         <v>2</v>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="F246" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19739,9 +20480,12 @@
         </is>
       </c>
       <c r="D247" s="4">
+        <v>3</v>
+      </c>
+      <c r="E247" s="4">
         <v>1</v>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="F247" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19802,9 +20546,12 @@
         </is>
       </c>
       <c r="D248" s="4">
+        <v>3</v>
+      </c>
+      <c r="E248" s="4">
         <v>2</v>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="F248" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19867,7 +20614,10 @@
       <c r="D249" s="4">
         <v>3</v>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="E249" s="4">
+        <v>3</v>
+      </c>
+      <c r="F249" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19930,7 +20680,10 @@
       <c r="D250" s="4">
         <v>1</v>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="E250" s="4">
+        <v>1</v>
+      </c>
+      <c r="F250" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -19958,7 +20711,10 @@
       <c r="D251" s="4">
         <v>1</v>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="E251" s="4">
+        <v>1</v>
+      </c>
+      <c r="F251" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20059,7 +20815,10 @@
       <c r="D252" s="4">
         <v>1</v>
       </c>
-      <c r="E252" s="6" t="inlineStr">
+      <c r="E252" s="4">
+        <v>1</v>
+      </c>
+      <c r="F252" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -20085,9 +20844,12 @@
         </is>
       </c>
       <c r="D253" s="4">
+        <v>8</v>
+      </c>
+      <c r="E253" s="4">
         <v>1</v>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="F253" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20186,9 +20948,12 @@
         </is>
       </c>
       <c r="D254" s="4">
+        <v>8</v>
+      </c>
+      <c r="E254" s="4">
         <v>2</v>
       </c>
-      <c r="E254" s="6" t="inlineStr">
+      <c r="F254" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20287,9 +21052,12 @@
         </is>
       </c>
       <c r="D255" s="4">
+        <v>8</v>
+      </c>
+      <c r="E255" s="4">
         <v>3</v>
       </c>
-      <c r="E255" s="6" t="inlineStr">
+      <c r="F255" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20388,9 +21156,12 @@
         </is>
       </c>
       <c r="D256" s="4">
+        <v>8</v>
+      </c>
+      <c r="E256" s="4">
         <v>4</v>
       </c>
-      <c r="E256" s="6" t="inlineStr">
+      <c r="F256" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20489,9 +21260,12 @@
         </is>
       </c>
       <c r="D257" s="4">
+        <v>4</v>
+      </c>
+      <c r="E257" s="4">
         <v>1</v>
       </c>
-      <c r="E257" s="6" t="inlineStr">
+      <c r="F257" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20597,9 +21371,12 @@
         </is>
       </c>
       <c r="D258" s="4">
+        <v>4</v>
+      </c>
+      <c r="E258" s="4">
         <v>2</v>
       </c>
-      <c r="E258" s="6" t="inlineStr">
+      <c r="F258" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20705,9 +21482,12 @@
         </is>
       </c>
       <c r="D259" s="4">
+        <v>4</v>
+      </c>
+      <c r="E259" s="4">
         <v>3</v>
       </c>
-      <c r="E259" s="6" t="inlineStr">
+      <c r="F259" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20815,7 +21595,10 @@
       <c r="D260" s="4">
         <v>1</v>
       </c>
-      <c r="E260" s="6" t="inlineStr">
+      <c r="E260" s="4">
+        <v>1</v>
+      </c>
+      <c r="F260" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -20841,9 +21624,12 @@
         </is>
       </c>
       <c r="D261" s="4">
+        <v>3</v>
+      </c>
+      <c r="E261" s="4">
         <v>1</v>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="F261" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -20869,9 +21655,12 @@
         </is>
       </c>
       <c r="D262" s="4">
+        <v>2</v>
+      </c>
+      <c r="E262" s="4">
         <v>1</v>
       </c>
-      <c r="E262" s="6" t="inlineStr">
+      <c r="F262" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -20897,9 +21686,12 @@
         </is>
       </c>
       <c r="D263" s="4">
+        <v>4</v>
+      </c>
+      <c r="E263" s="4">
         <v>1</v>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="F263" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21013,9 +21805,12 @@
         </is>
       </c>
       <c r="D264" s="4">
+        <v>6</v>
+      </c>
+      <c r="E264" s="4">
         <v>1</v>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="F264" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21129,9 +21924,12 @@
         </is>
       </c>
       <c r="D265" s="4">
+        <v>6</v>
+      </c>
+      <c r="E265" s="4">
         <v>2</v>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="F265" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21245,9 +22043,12 @@
         </is>
       </c>
       <c r="D266" s="4">
+        <v>6</v>
+      </c>
+      <c r="E266" s="4">
         <v>3</v>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21361,9 +22162,12 @@
         </is>
       </c>
       <c r="D267" s="4">
+        <v>6</v>
+      </c>
+      <c r="E267" s="4">
         <v>4</v>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21477,9 +22281,12 @@
         </is>
       </c>
       <c r="D268" s="4">
+        <v>6</v>
+      </c>
+      <c r="E268" s="4">
         <v>1</v>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="F268" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21600,9 +22407,12 @@
         </is>
       </c>
       <c r="D269" s="4">
+        <v>6</v>
+      </c>
+      <c r="E269" s="4">
         <v>2</v>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21723,9 +22533,12 @@
         </is>
       </c>
       <c r="D270" s="4">
+        <v>6</v>
+      </c>
+      <c r="E270" s="4">
         <v>3</v>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21846,9 +22659,12 @@
         </is>
       </c>
       <c r="D271" s="4">
+        <v>7</v>
+      </c>
+      <c r="E271" s="4">
         <v>1</v>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21969,9 +22785,12 @@
         </is>
       </c>
       <c r="D272" s="4">
+        <v>7</v>
+      </c>
+      <c r="E272" s="4">
         <v>2</v>
       </c>
-      <c r="E272" s="6" t="inlineStr">
+      <c r="F272" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22092,9 +22911,12 @@
         </is>
       </c>
       <c r="D273" s="4">
+        <v>7</v>
+      </c>
+      <c r="E273" s="4">
         <v>3</v>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="F273" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22215,9 +23037,12 @@
         </is>
       </c>
       <c r="D274" s="4">
+        <v>7</v>
+      </c>
+      <c r="E274" s="4">
         <v>4</v>
       </c>
-      <c r="E274" s="6" t="inlineStr">
+      <c r="F274" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22338,9 +23163,12 @@
         </is>
       </c>
       <c r="D275" s="4">
+        <v>7</v>
+      </c>
+      <c r="E275" s="4">
         <v>5</v>
       </c>
-      <c r="E275" s="6" t="inlineStr">
+      <c r="F275" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22461,9 +23289,12 @@
         </is>
       </c>
       <c r="D276" s="4">
+        <v>4</v>
+      </c>
+      <c r="E276" s="4">
         <v>1</v>
       </c>
-      <c r="E276" s="6" t="inlineStr">
+      <c r="F276" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -22489,9 +23320,12 @@
         </is>
       </c>
       <c r="D277" s="4">
+        <v>5</v>
+      </c>
+      <c r="E277" s="4">
         <v>1</v>
       </c>
-      <c r="E277" s="6" t="inlineStr">
+      <c r="F277" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22545,9 +23379,12 @@
         </is>
       </c>
       <c r="D278" s="4">
+        <v>5</v>
+      </c>
+      <c r="E278" s="4">
         <v>2</v>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="F278" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22601,9 +23438,12 @@
         </is>
       </c>
       <c r="D279" s="4">
+        <v>5</v>
+      </c>
+      <c r="E279" s="4">
         <v>3</v>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="F279" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22657,9 +23497,12 @@
         </is>
       </c>
       <c r="D280" s="4">
+        <v>5</v>
+      </c>
+      <c r="E280" s="4">
         <v>4</v>
       </c>
-      <c r="E280" s="6" t="inlineStr">
+      <c r="F280" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22715,7 +23558,10 @@
       <c r="D281" s="4">
         <v>5</v>
       </c>
-      <c r="E281" s="6" t="inlineStr">
+      <c r="E281" s="4">
+        <v>5</v>
+      </c>
+      <c r="F281" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22769,9 +23615,12 @@
         </is>
       </c>
       <c r="D282" s="4">
+        <v>3</v>
+      </c>
+      <c r="E282" s="4">
         <v>1</v>
       </c>
-      <c r="E282" s="6" t="inlineStr">
+      <c r="F282" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22825,9 +23674,12 @@
         </is>
       </c>
       <c r="D283" s="4">
+        <v>3</v>
+      </c>
+      <c r="E283" s="4">
         <v>2</v>
       </c>
-      <c r="E283" s="6" t="inlineStr">
+      <c r="F283" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22883,7 +23735,10 @@
       <c r="D284" s="4">
         <v>3</v>
       </c>
-      <c r="E284" s="6" t="inlineStr">
+      <c r="E284" s="4">
+        <v>3</v>
+      </c>
+      <c r="F284" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22937,9 +23792,12 @@
         </is>
       </c>
       <c r="D285" s="4">
+        <v>3</v>
+      </c>
+      <c r="E285" s="4">
         <v>1</v>
       </c>
-      <c r="E285" s="6" t="inlineStr">
+      <c r="F285" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22993,9 +23851,12 @@
         </is>
       </c>
       <c r="D286" s="4">
+        <v>3</v>
+      </c>
+      <c r="E286" s="4">
         <v>2</v>
       </c>
-      <c r="E286" s="6" t="inlineStr">
+      <c r="F286" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23051,7 +23912,10 @@
       <c r="D287" s="4">
         <v>3</v>
       </c>
-      <c r="E287" s="6" t="inlineStr">
+      <c r="E287" s="4">
+        <v>3</v>
+      </c>
+      <c r="F287" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23105,9 +23969,12 @@
         </is>
       </c>
       <c r="D288" s="4">
+        <v>3</v>
+      </c>
+      <c r="E288" s="4">
         <v>1</v>
       </c>
-      <c r="E288" s="6" t="inlineStr">
+      <c r="F288" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23161,9 +24028,12 @@
         </is>
       </c>
       <c r="D289" s="4">
+        <v>3</v>
+      </c>
+      <c r="E289" s="4">
         <v>2</v>
       </c>
-      <c r="E289" s="6" t="inlineStr">
+      <c r="F289" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23219,7 +24089,10 @@
       <c r="D290" s="4">
         <v>3</v>
       </c>
-      <c r="E290" s="6" t="inlineStr">
+      <c r="E290" s="4">
+        <v>3</v>
+      </c>
+      <c r="F290" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23275,7 +24148,10 @@
       <c r="D291" s="4">
         <v>1</v>
       </c>
-      <c r="E291" s="6" t="inlineStr">
+      <c r="E291" s="4">
+        <v>1</v>
+      </c>
+      <c r="F291" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23329,9 +24205,12 @@
         </is>
       </c>
       <c r="D292" s="4">
+        <v>2</v>
+      </c>
+      <c r="E292" s="4">
         <v>1</v>
       </c>
-      <c r="E292" s="6" t="inlineStr">
+      <c r="F292" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23387,7 +24266,10 @@
       <c r="D293" s="4">
         <v>2</v>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="E293" s="4">
+        <v>2</v>
+      </c>
+      <c r="F293" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23443,7 +24325,10 @@
       <c r="D294" s="4">
         <v>1</v>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="E294" s="4">
+        <v>1</v>
+      </c>
+      <c r="F294" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23497,9 +24382,12 @@
         </is>
       </c>
       <c r="D295" s="4">
+        <v>6</v>
+      </c>
+      <c r="E295" s="4">
         <v>1</v>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="F295" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23553,9 +24441,12 @@
         </is>
       </c>
       <c r="D296" s="4">
+        <v>6</v>
+      </c>
+      <c r="E296" s="4">
         <v>2</v>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23609,9 +24500,12 @@
         </is>
       </c>
       <c r="D297" s="4">
+        <v>6</v>
+      </c>
+      <c r="E297" s="4">
         <v>3</v>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23665,9 +24559,12 @@
         </is>
       </c>
       <c r="D298" s="4">
+        <v>6</v>
+      </c>
+      <c r="E298" s="4">
         <v>4</v>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23721,9 +24618,12 @@
         </is>
       </c>
       <c r="D299" s="4">
+        <v>6</v>
+      </c>
+      <c r="E299" s="4">
         <v>5</v>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="F299" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23779,7 +24679,10 @@
       <c r="D300" s="4">
         <v>6</v>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="E300" s="4">
+        <v>6</v>
+      </c>
+      <c r="F300" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23833,9 +24736,12 @@
         </is>
       </c>
       <c r="D301" s="4">
+        <v>4</v>
+      </c>
+      <c r="E301" s="4">
         <v>1</v>
       </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="F301" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23889,9 +24795,12 @@
         </is>
       </c>
       <c r="D302" s="4">
+        <v>4</v>
+      </c>
+      <c r="E302" s="4">
         <v>2</v>
       </c>
-      <c r="E302" s="6" t="inlineStr">
+      <c r="F302" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23945,9 +24854,12 @@
         </is>
       </c>
       <c r="D303" s="4">
+        <v>4</v>
+      </c>
+      <c r="E303" s="4">
         <v>3</v>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="F303" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24003,7 +24915,10 @@
       <c r="D304" s="4">
         <v>4</v>
       </c>
-      <c r="E304" s="6" t="inlineStr">
+      <c r="E304" s="4">
+        <v>4</v>
+      </c>
+      <c r="F304" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24057,9 +24972,12 @@
         </is>
       </c>
       <c r="D305" s="4">
+        <v>2</v>
+      </c>
+      <c r="E305" s="4">
         <v>1</v>
       </c>
-      <c r="E305" s="6" t="inlineStr">
+      <c r="F305" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24115,7 +25033,10 @@
       <c r="D306" s="4">
         <v>2</v>
       </c>
-      <c r="E306" s="6" t="inlineStr">
+      <c r="E306" s="4">
+        <v>2</v>
+      </c>
+      <c r="F306" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24169,9 +25090,12 @@
         </is>
       </c>
       <c r="D307" s="4">
+        <v>3</v>
+      </c>
+      <c r="E307" s="4">
         <v>1</v>
       </c>
-      <c r="E307" s="6" t="inlineStr">
+      <c r="F307" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24225,9 +25149,12 @@
         </is>
       </c>
       <c r="D308" s="4">
+        <v>3</v>
+      </c>
+      <c r="E308" s="4">
         <v>2</v>
       </c>
-      <c r="E308" s="6" t="inlineStr">
+      <c r="F308" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24283,7 +25210,10 @@
       <c r="D309" s="4">
         <v>3</v>
       </c>
-      <c r="E309" s="6" t="inlineStr">
+      <c r="E309" s="4">
+        <v>3</v>
+      </c>
+      <c r="F309" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24339,7 +25269,10 @@
       <c r="D310" s="4">
         <v>1</v>
       </c>
-      <c r="E310" s="6" t="inlineStr">
+      <c r="E310" s="4">
+        <v>1</v>
+      </c>
+      <c r="F310" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24393,9 +25326,12 @@
         </is>
       </c>
       <c r="D311" s="4">
+        <v>5</v>
+      </c>
+      <c r="E311" s="4">
         <v>1</v>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="F311" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24449,9 +25385,12 @@
         </is>
       </c>
       <c r="D312" s="4">
+        <v>5</v>
+      </c>
+      <c r="E312" s="4">
         <v>2</v>
       </c>
-      <c r="E312" s="6" t="inlineStr">
+      <c r="F312" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24505,9 +25444,12 @@
         </is>
       </c>
       <c r="D313" s="4">
+        <v>5</v>
+      </c>
+      <c r="E313" s="4">
         <v>3</v>
       </c>
-      <c r="E313" s="6" t="inlineStr">
+      <c r="F313" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24561,9 +25503,12 @@
         </is>
       </c>
       <c r="D314" s="4">
+        <v>5</v>
+      </c>
+      <c r="E314" s="4">
         <v>4</v>
       </c>
-      <c r="E314" s="6" t="inlineStr">
+      <c r="F314" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24619,7 +25564,10 @@
       <c r="D315" s="4">
         <v>5</v>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="E315" s="4">
+        <v>5</v>
+      </c>
+      <c r="F315" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24673,9 +25621,12 @@
         </is>
       </c>
       <c r="D316" s="4">
+        <v>3</v>
+      </c>
+      <c r="E316" s="4">
         <v>1</v>
       </c>
-      <c r="E316" s="6" t="inlineStr">
+      <c r="F316" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24729,9 +25680,12 @@
         </is>
       </c>
       <c r="D317" s="4">
+        <v>3</v>
+      </c>
+      <c r="E317" s="4">
         <v>2</v>
       </c>
-      <c r="E317" s="6" t="inlineStr">
+      <c r="F317" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24787,7 +25741,10 @@
       <c r="D318" s="4">
         <v>3</v>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="E318" s="4">
+        <v>3</v>
+      </c>
+      <c r="F318" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24841,9 +25798,12 @@
         </is>
       </c>
       <c r="D319" s="4">
+        <v>2</v>
+      </c>
+      <c r="E319" s="4">
         <v>1</v>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="F319" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24899,7 +25859,10 @@
       <c r="D320" s="4">
         <v>2</v>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="E320" s="4">
+        <v>2</v>
+      </c>
+      <c r="F320" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24955,7 +25918,10 @@
       <c r="D321" s="4">
         <v>1</v>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="E321" s="4">
+        <v>1</v>
+      </c>
+      <c r="F321" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25009,9 +25975,12 @@
         </is>
       </c>
       <c r="D322" s="4">
+        <v>8</v>
+      </c>
+      <c r="E322" s="4">
         <v>1</v>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="F322" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25065,9 +26034,12 @@
         </is>
       </c>
       <c r="D323" s="4">
+        <v>8</v>
+      </c>
+      <c r="E323" s="4">
         <v>2</v>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="F323" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25121,9 +26093,12 @@
         </is>
       </c>
       <c r="D324" s="4">
+        <v>8</v>
+      </c>
+      <c r="E324" s="4">
         <v>3</v>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="F324" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25177,9 +26152,12 @@
         </is>
       </c>
       <c r="D325" s="4">
+        <v>8</v>
+      </c>
+      <c r="E325" s="4">
         <v>4</v>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25233,9 +26211,12 @@
         </is>
       </c>
       <c r="D326" s="4">
+        <v>8</v>
+      </c>
+      <c r="E326" s="4">
         <v>5</v>
       </c>
-      <c r="E326" s="6" t="inlineStr">
+      <c r="F326" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25289,9 +26270,12 @@
         </is>
       </c>
       <c r="D327" s="4">
+        <v>8</v>
+      </c>
+      <c r="E327" s="4">
         <v>6</v>
       </c>
-      <c r="E327" s="6" t="inlineStr">
+      <c r="F327" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25345,9 +26329,12 @@
         </is>
       </c>
       <c r="D328" s="4">
+        <v>8</v>
+      </c>
+      <c r="E328" s="4">
         <v>7</v>
       </c>
-      <c r="E328" s="6" t="inlineStr">
+      <c r="F328" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25403,7 +26390,10 @@
       <c r="D329" s="4">
         <v>8</v>
       </c>
-      <c r="E329" s="6" t="inlineStr">
+      <c r="E329" s="4">
+        <v>8</v>
+      </c>
+      <c r="F329" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25457,9 +26447,12 @@
         </is>
       </c>
       <c r="D330" s="4">
+        <v>4</v>
+      </c>
+      <c r="E330" s="4">
         <v>1</v>
       </c>
-      <c r="E330" s="6" t="inlineStr">
+      <c r="F330" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25529,9 +26522,12 @@
         </is>
       </c>
       <c r="D331" s="4">
+        <v>4</v>
+      </c>
+      <c r="E331" s="4">
         <v>2</v>
       </c>
-      <c r="E331" s="6" t="inlineStr">
+      <c r="F331" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25601,9 +26597,12 @@
         </is>
       </c>
       <c r="D332" s="4">
+        <v>4</v>
+      </c>
+      <c r="E332" s="4">
         <v>3</v>
       </c>
-      <c r="E332" s="6" t="inlineStr">
+      <c r="F332" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25675,7 +26674,10 @@
       <c r="D333" s="4">
         <v>4</v>
       </c>
-      <c r="E333" s="6" t="inlineStr">
+      <c r="E333" s="4">
+        <v>4</v>
+      </c>
+      <c r="F333" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25745,9 +26747,12 @@
         </is>
       </c>
       <c r="D334" s="4">
+        <v>14</v>
+      </c>
+      <c r="E334" s="4">
         <v>1</v>
       </c>
-      <c r="E334" s="6" t="inlineStr">
+      <c r="F334" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25808,9 +26813,12 @@
         </is>
       </c>
       <c r="D335" s="4">
+        <v>14</v>
+      </c>
+      <c r="E335" s="4">
         <v>2</v>
       </c>
-      <c r="E335" s="6" t="inlineStr">
+      <c r="F335" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25871,9 +26879,12 @@
         </is>
       </c>
       <c r="D336" s="4">
+        <v>14</v>
+      </c>
+      <c r="E336" s="4">
         <v>3</v>
       </c>
-      <c r="E336" s="6" t="inlineStr">
+      <c r="F336" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25934,9 +26945,12 @@
         </is>
       </c>
       <c r="D337" s="4">
+        <v>14</v>
+      </c>
+      <c r="E337" s="4">
         <v>4</v>
       </c>
-      <c r="E337" s="6" t="inlineStr">
+      <c r="F337" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25997,9 +27011,12 @@
         </is>
       </c>
       <c r="D338" s="4">
+        <v>14</v>
+      </c>
+      <c r="E338" s="4">
         <v>5</v>
       </c>
-      <c r="E338" s="6" t="inlineStr">
+      <c r="F338" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26060,9 +27077,12 @@
         </is>
       </c>
       <c r="D339" s="4">
+        <v>14</v>
+      </c>
+      <c r="E339" s="4">
         <v>6</v>
       </c>
-      <c r="E339" s="6" t="inlineStr">
+      <c r="F339" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26123,9 +27143,12 @@
         </is>
       </c>
       <c r="D340" s="4">
+        <v>14</v>
+      </c>
+      <c r="E340" s="4">
         <v>7</v>
       </c>
-      <c r="E340" s="6" t="inlineStr">
+      <c r="F340" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26186,9 +27209,12 @@
         </is>
       </c>
       <c r="D341" s="4">
+        <v>14</v>
+      </c>
+      <c r="E341" s="4">
         <v>8</v>
       </c>
-      <c r="E341" s="6" t="inlineStr">
+      <c r="F341" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26249,9 +27275,12 @@
         </is>
       </c>
       <c r="D342" s="4">
+        <v>14</v>
+      </c>
+      <c r="E342" s="4">
         <v>9</v>
       </c>
-      <c r="E342" s="6" t="inlineStr">
+      <c r="F342" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26312,9 +27341,12 @@
         </is>
       </c>
       <c r="D343" s="4">
+        <v>14</v>
+      </c>
+      <c r="E343" s="4">
         <v>10</v>
       </c>
-      <c r="E343" s="6" t="inlineStr">
+      <c r="F343" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26375,9 +27407,12 @@
         </is>
       </c>
       <c r="D344" s="4">
+        <v>14</v>
+      </c>
+      <c r="E344" s="4">
         <v>11</v>
       </c>
-      <c r="E344" s="6" t="inlineStr">
+      <c r="F344" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26438,9 +27473,12 @@
         </is>
       </c>
       <c r="D345" s="4">
+        <v>14</v>
+      </c>
+      <c r="E345" s="4">
         <v>12</v>
       </c>
-      <c r="E345" s="6" t="inlineStr">
+      <c r="F345" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26501,9 +27539,12 @@
         </is>
       </c>
       <c r="D346" s="4">
+        <v>14</v>
+      </c>
+      <c r="E346" s="4">
         <v>13</v>
       </c>
-      <c r="E346" s="6" t="inlineStr">
+      <c r="F346" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26566,7 +27607,10 @@
       <c r="D347" s="4">
         <v>14</v>
       </c>
-      <c r="E347" s="6" t="inlineStr">
+      <c r="E347" s="4">
+        <v>14</v>
+      </c>
+      <c r="F347" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26627,9 +27671,12 @@
         </is>
       </c>
       <c r="D348" s="4">
+        <v>9</v>
+      </c>
+      <c r="E348" s="4">
         <v>1</v>
       </c>
-      <c r="E348" s="6" t="inlineStr">
+      <c r="F348" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26690,9 +27737,12 @@
         </is>
       </c>
       <c r="D349" s="4">
+        <v>9</v>
+      </c>
+      <c r="E349" s="4">
         <v>2</v>
       </c>
-      <c r="E349" s="6" t="inlineStr">
+      <c r="F349" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26753,9 +27803,12 @@
         </is>
       </c>
       <c r="D350" s="4">
+        <v>9</v>
+      </c>
+      <c r="E350" s="4">
         <v>3</v>
       </c>
-      <c r="E350" s="6" t="inlineStr">
+      <c r="F350" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26816,9 +27869,12 @@
         </is>
       </c>
       <c r="D351" s="4">
+        <v>9</v>
+      </c>
+      <c r="E351" s="4">
         <v>4</v>
       </c>
-      <c r="E351" s="6" t="inlineStr">
+      <c r="F351" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26879,9 +27935,12 @@
         </is>
       </c>
       <c r="D352" s="4">
+        <v>9</v>
+      </c>
+      <c r="E352" s="4">
         <v>5</v>
       </c>
-      <c r="E352" s="6" t="inlineStr">
+      <c r="F352" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26942,9 +28001,12 @@
         </is>
       </c>
       <c r="D353" s="4">
+        <v>9</v>
+      </c>
+      <c r="E353" s="4">
         <v>6</v>
       </c>
-      <c r="E353" s="6" t="inlineStr">
+      <c r="F353" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27005,9 +28067,12 @@
         </is>
       </c>
       <c r="D354" s="4">
+        <v>9</v>
+      </c>
+      <c r="E354" s="4">
         <v>7</v>
       </c>
-      <c r="E354" s="6" t="inlineStr">
+      <c r="F354" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27076,9 +28141,12 @@
         </is>
       </c>
       <c r="D355" s="4">
+        <v>9</v>
+      </c>
+      <c r="E355" s="4">
         <v>8</v>
       </c>
-      <c r="E355" s="6" t="inlineStr">
+      <c r="F355" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27141,7 +28209,10 @@
       <c r="D356" s="4">
         <v>9</v>
       </c>
-      <c r="E356" s="6" t="inlineStr">
+      <c r="E356" s="4">
+        <v>9</v>
+      </c>
+      <c r="F356" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27202,9 +28273,12 @@
         </is>
       </c>
       <c r="D357" s="4">
+        <v>2</v>
+      </c>
+      <c r="E357" s="4">
         <v>1</v>
       </c>
-      <c r="E357" s="6" t="inlineStr">
+      <c r="F357" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27267,7 +28341,10 @@
       <c r="D358" s="4">
         <v>2</v>
       </c>
-      <c r="E358" s="6" t="inlineStr">
+      <c r="E358" s="4">
+        <v>2</v>
+      </c>
+      <c r="F358" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27330,7 +28407,10 @@
       <c r="D359" s="4">
         <v>1</v>
       </c>
-      <c r="E359" s="6" t="inlineStr">
+      <c r="E359" s="4">
+        <v>1</v>
+      </c>
+      <c r="F359" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27401,7 +28481,10 @@
       <c r="D360" s="4">
         <v>1</v>
       </c>
-      <c r="E360" s="6" t="inlineStr">
+      <c r="E360" s="4">
+        <v>1</v>
+      </c>
+      <c r="F360" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27477,9 +28560,12 @@
         </is>
       </c>
       <c r="D361" s="4">
+        <v>52</v>
+      </c>
+      <c r="E361" s="4">
         <v>1</v>
       </c>
-      <c r="E361" s="6" t="inlineStr">
+      <c r="F361" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27660,9 +28746,12 @@
         </is>
       </c>
       <c r="D362" s="4">
+        <v>52</v>
+      </c>
+      <c r="E362" s="4">
         <v>2</v>
       </c>
-      <c r="E362" s="6" t="inlineStr">
+      <c r="F362" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27798,9 +28887,12 @@
         </is>
       </c>
       <c r="D363" s="4">
+        <v>52</v>
+      </c>
+      <c r="E363" s="4">
         <v>3</v>
       </c>
-      <c r="E363" s="6" t="inlineStr">
+      <c r="F363" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27929,9 +29021,12 @@
         </is>
       </c>
       <c r="D364" s="4">
+        <v>52</v>
+      </c>
+      <c r="E364" s="4">
         <v>4</v>
       </c>
-      <c r="E364" s="6" t="inlineStr">
+      <c r="F364" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28045,9 +29140,12 @@
         </is>
       </c>
       <c r="D365" s="4">
+        <v>52</v>
+      </c>
+      <c r="E365" s="4">
         <v>5</v>
       </c>
-      <c r="E365" s="6" t="inlineStr">
+      <c r="F365" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28161,9 +29259,12 @@
         </is>
       </c>
       <c r="D366" s="4">
+        <v>52</v>
+      </c>
+      <c r="E366" s="4">
         <v>6</v>
       </c>
-      <c r="E366" s="6" t="inlineStr">
+      <c r="F366" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28284,9 +29385,12 @@
         </is>
       </c>
       <c r="D367" s="4">
+        <v>52</v>
+      </c>
+      <c r="E367" s="4">
         <v>7</v>
       </c>
-      <c r="E367" s="6" t="inlineStr">
+      <c r="F367" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28445,9 +29549,12 @@
         </is>
       </c>
       <c r="D368" s="4">
+        <v>52</v>
+      </c>
+      <c r="E368" s="4">
         <v>8</v>
       </c>
-      <c r="E368" s="6" t="inlineStr">
+      <c r="F368" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28561,9 +29668,12 @@
         </is>
       </c>
       <c r="D369" s="4">
+        <v>52</v>
+      </c>
+      <c r="E369" s="4">
         <v>9</v>
       </c>
-      <c r="E369" s="6" t="inlineStr">
+      <c r="F369" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28692,9 +29802,12 @@
         </is>
       </c>
       <c r="D370" s="4">
+        <v>52</v>
+      </c>
+      <c r="E370" s="4">
         <v>10</v>
       </c>
-      <c r="E370" s="6" t="inlineStr">
+      <c r="F370" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28830,9 +29943,12 @@
         </is>
       </c>
       <c r="D371" s="4">
+        <v>52</v>
+      </c>
+      <c r="E371" s="4">
         <v>11</v>
       </c>
-      <c r="E371" s="6" t="inlineStr">
+      <c r="F371" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28976,9 +30092,12 @@
         </is>
       </c>
       <c r="D372" s="4">
+        <v>52</v>
+      </c>
+      <c r="E372" s="4">
         <v>12</v>
       </c>
-      <c r="E372" s="6" t="inlineStr">
+      <c r="F372" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29084,9 +30203,12 @@
         </is>
       </c>
       <c r="D373" s="4">
+        <v>52</v>
+      </c>
+      <c r="E373" s="4">
         <v>13</v>
       </c>
-      <c r="E373" s="6" t="inlineStr">
+      <c r="F373" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29267,9 +30389,12 @@
         </is>
       </c>
       <c r="D374" s="4">
+        <v>52</v>
+      </c>
+      <c r="E374" s="4">
         <v>14</v>
       </c>
-      <c r="E374" s="6" t="inlineStr">
+      <c r="F374" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29435,9 +30560,12 @@
         </is>
       </c>
       <c r="D375" s="4">
+        <v>52</v>
+      </c>
+      <c r="E375" s="4">
         <v>15</v>
       </c>
-      <c r="E375" s="6" t="inlineStr">
+      <c r="F375" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29566,9 +30694,12 @@
         </is>
       </c>
       <c r="D376" s="4">
+        <v>52</v>
+      </c>
+      <c r="E376" s="4">
         <v>16</v>
       </c>
-      <c r="E376" s="6" t="inlineStr">
+      <c r="F376" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29757,9 +30888,12 @@
         </is>
       </c>
       <c r="D377" s="4">
+        <v>52</v>
+      </c>
+      <c r="E377" s="4">
         <v>17</v>
       </c>
-      <c r="E377" s="6" t="inlineStr">
+      <c r="F377" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29888,9 +31022,12 @@
         </is>
       </c>
       <c r="D378" s="4">
+        <v>52</v>
+      </c>
+      <c r="E378" s="4">
         <v>18</v>
       </c>
-      <c r="E378" s="6" t="inlineStr">
+      <c r="F378" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30011,9 +31148,12 @@
         </is>
       </c>
       <c r="D379" s="4">
+        <v>52</v>
+      </c>
+      <c r="E379" s="4">
         <v>19</v>
       </c>
-      <c r="E379" s="6" t="inlineStr">
+      <c r="F379" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30149,9 +31289,12 @@
         </is>
       </c>
       <c r="D380" s="4">
+        <v>52</v>
+      </c>
+      <c r="E380" s="4">
         <v>20</v>
       </c>
-      <c r="E380" s="6" t="inlineStr">
+      <c r="F380" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30349,7 +31492,10 @@
       <c r="D381" s="4">
         <v>1</v>
       </c>
-      <c r="E381" s="6" t="inlineStr">
+      <c r="E381" s="4">
+        <v>1</v>
+      </c>
+      <c r="F381" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30419,9 +31565,12 @@
         </is>
       </c>
       <c r="D382" s="4">
+        <v>4</v>
+      </c>
+      <c r="E382" s="4">
         <v>1</v>
       </c>
-      <c r="E382" s="6" t="inlineStr">
+      <c r="F382" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30491,9 +31640,12 @@
         </is>
       </c>
       <c r="D383" s="4">
+        <v>4</v>
+      </c>
+      <c r="E383" s="4">
         <v>2</v>
       </c>
-      <c r="E383" s="6" t="inlineStr">
+      <c r="F383" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30554,9 +31706,12 @@
         </is>
       </c>
       <c r="D384" s="4">
+        <v>4</v>
+      </c>
+      <c r="E384" s="4">
         <v>3</v>
       </c>
-      <c r="E384" s="6" t="inlineStr">
+      <c r="F384" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30628,7 +31783,10 @@
       <c r="D385" s="4">
         <v>4</v>
       </c>
-      <c r="E385" s="6" t="inlineStr">
+      <c r="E385" s="4">
+        <v>4</v>
+      </c>
+      <c r="F385" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30698,9 +31856,12 @@
         </is>
       </c>
       <c r="D386" s="4">
+        <v>3</v>
+      </c>
+      <c r="E386" s="4">
         <v>1</v>
       </c>
-      <c r="E386" s="6" t="inlineStr">
+      <c r="F386" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30761,9 +31922,12 @@
         </is>
       </c>
       <c r="D387" s="4">
+        <v>3</v>
+      </c>
+      <c r="E387" s="4">
         <v>2</v>
       </c>
-      <c r="E387" s="6" t="inlineStr">
+      <c r="F387" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30826,7 +31990,10 @@
       <c r="D388" s="4">
         <v>3</v>
       </c>
-      <c r="E388" s="6" t="inlineStr">
+      <c r="E388" s="4">
+        <v>3</v>
+      </c>
+      <c r="F388" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30887,9 +32054,12 @@
         </is>
       </c>
       <c r="D389" s="4">
+        <v>2</v>
+      </c>
+      <c r="E389" s="4">
         <v>1</v>
       </c>
-      <c r="E389" s="6" t="inlineStr">
+      <c r="F389" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30960,7 +32130,10 @@
       <c r="D390" s="4">
         <v>2</v>
       </c>
-      <c r="E390" s="6" t="inlineStr">
+      <c r="E390" s="4">
+        <v>2</v>
+      </c>
+      <c r="F390" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31029,9 +32202,12 @@
         </is>
       </c>
       <c r="D391" s="4">
+        <v>5</v>
+      </c>
+      <c r="E391" s="4">
         <v>1</v>
       </c>
-      <c r="E391" s="6" t="inlineStr">
+      <c r="F391" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31101,9 +32277,12 @@
         </is>
       </c>
       <c r="D392" s="4">
+        <v>5</v>
+      </c>
+      <c r="E392" s="4">
         <v>2</v>
       </c>
-      <c r="E392" s="6" t="inlineStr">
+      <c r="F392" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31164,9 +32343,12 @@
         </is>
       </c>
       <c r="D393" s="4">
+        <v>5</v>
+      </c>
+      <c r="E393" s="4">
         <v>3</v>
       </c>
-      <c r="E393" s="6" t="inlineStr">
+      <c r="F393" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31236,9 +32418,12 @@
         </is>
       </c>
       <c r="D394" s="4">
+        <v>5</v>
+      </c>
+      <c r="E394" s="4">
         <v>4</v>
       </c>
-      <c r="E394" s="6" t="inlineStr">
+      <c r="F394" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31310,7 +32495,10 @@
       <c r="D395" s="4">
         <v>5</v>
       </c>
-      <c r="E395" s="6" t="inlineStr">
+      <c r="E395" s="4">
+        <v>5</v>
+      </c>
+      <c r="F395" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31382,7 +32570,10 @@
       <c r="D396" s="4">
         <v>1</v>
       </c>
-      <c r="E396" s="6" t="inlineStr">
+      <c r="E396" s="4">
+        <v>1</v>
+      </c>
+      <c r="F396" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31443,9 +32634,12 @@
         </is>
       </c>
       <c r="D397" s="4">
+        <v>5</v>
+      </c>
+      <c r="E397" s="4">
         <v>1</v>
       </c>
-      <c r="E397" s="6" t="inlineStr">
+      <c r="F397" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31506,9 +32700,12 @@
         </is>
       </c>
       <c r="D398" s="4">
+        <v>5</v>
+      </c>
+      <c r="E398" s="4">
         <v>2</v>
       </c>
-      <c r="E398" s="6" t="inlineStr">
+      <c r="F398" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31569,9 +32766,12 @@
         </is>
       </c>
       <c r="D399" s="4">
+        <v>5</v>
+      </c>
+      <c r="E399" s="4">
         <v>3</v>
       </c>
-      <c r="E399" s="6" t="inlineStr">
+      <c r="F399" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31632,9 +32832,12 @@
         </is>
       </c>
       <c r="D400" s="4">
+        <v>5</v>
+      </c>
+      <c r="E400" s="4">
         <v>4</v>
       </c>
-      <c r="E400" s="6" t="inlineStr">
+      <c r="F400" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31697,7 +32900,10 @@
       <c r="D401" s="4">
         <v>1</v>
       </c>
-      <c r="E401" s="6" t="inlineStr">
+      <c r="E401" s="4">
+        <v>1</v>
+      </c>
+      <c r="F401" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31766,9 +32972,12 @@
         </is>
       </c>
       <c r="D402" s="4">
+        <v>2</v>
+      </c>
+      <c r="E402" s="4">
         <v>1</v>
       </c>
-      <c r="E402" s="6" t="inlineStr">
+      <c r="F402" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31854,7 +33063,10 @@
       <c r="D403" s="4">
         <v>2</v>
       </c>
-      <c r="E403" s="6" t="inlineStr">
+      <c r="E403" s="4">
+        <v>2</v>
+      </c>
+      <c r="F403" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31955,7 +33167,10 @@
       <c r="D404" s="4">
         <v>1</v>
       </c>
-      <c r="E404" s="6" t="inlineStr">
+      <c r="E404" s="4">
+        <v>1</v>
+      </c>
+      <c r="F404" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32025,9 +33240,12 @@
         </is>
       </c>
       <c r="D405" s="4">
+        <v>2</v>
+      </c>
+      <c r="E405" s="4">
         <v>1</v>
       </c>
-      <c r="E405" s="6" t="inlineStr">
+      <c r="F405" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32098,7 +33316,10 @@
       <c r="D406" s="4">
         <v>2</v>
       </c>
-      <c r="E406" s="6" t="inlineStr">
+      <c r="E406" s="4">
+        <v>2</v>
+      </c>
+      <c r="F406" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32167,9 +33388,12 @@
         </is>
       </c>
       <c r="D407" s="4">
+        <v>3</v>
+      </c>
+      <c r="E407" s="4">
         <v>1</v>
       </c>
-      <c r="E407" s="6" t="inlineStr">
+      <c r="F407" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32238,9 +33462,12 @@
         </is>
       </c>
       <c r="D408" s="4">
+        <v>3</v>
+      </c>
+      <c r="E408" s="4">
         <v>2</v>
       </c>
-      <c r="E408" s="6" t="inlineStr">
+      <c r="F408" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32311,7 +33538,10 @@
       <c r="D409" s="4">
         <v>3</v>
       </c>
-      <c r="E409" s="6" t="inlineStr">
+      <c r="E409" s="4">
+        <v>3</v>
+      </c>
+      <c r="F409" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32387,9 +33617,12 @@
         </is>
       </c>
       <c r="D410" s="4">
+        <v>5</v>
+      </c>
+      <c r="E410" s="4">
         <v>1</v>
       </c>
-      <c r="E410" s="6" t="inlineStr">
+      <c r="F410" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32450,9 +33683,12 @@
         </is>
       </c>
       <c r="D411" s="4">
+        <v>5</v>
+      </c>
+      <c r="E411" s="4">
         <v>2</v>
       </c>
-      <c r="E411" s="6" t="inlineStr">
+      <c r="F411" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32558,9 +33794,12 @@
         </is>
       </c>
       <c r="D412" s="4">
+        <v>5</v>
+      </c>
+      <c r="E412" s="4">
         <v>3</v>
       </c>
-      <c r="E412" s="6" t="inlineStr">
+      <c r="F412" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32629,9 +33868,12 @@
         </is>
       </c>
       <c r="D413" s="4">
+        <v>5</v>
+      </c>
+      <c r="E413" s="4">
         <v>4</v>
       </c>
-      <c r="E413" s="6" t="inlineStr">
+      <c r="F413" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32694,7 +33936,10 @@
       <c r="D414" s="4">
         <v>5</v>
       </c>
-      <c r="E414" s="6" t="inlineStr">
+      <c r="E414" s="4">
+        <v>5</v>
+      </c>
+      <c r="F414" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32763,9 +34008,12 @@
         </is>
       </c>
       <c r="D415" s="4">
+        <v>3</v>
+      </c>
+      <c r="E415" s="4">
         <v>1</v>
       </c>
-      <c r="E415" s="6" t="inlineStr">
+      <c r="F415" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32826,9 +34074,12 @@
         </is>
       </c>
       <c r="D416" s="4">
+        <v>3</v>
+      </c>
+      <c r="E416" s="4">
         <v>2</v>
       </c>
-      <c r="E416" s="6" t="inlineStr">
+      <c r="F416" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32891,7 +34142,10 @@
       <c r="D417" s="4">
         <v>3</v>
       </c>
-      <c r="E417" s="6" t="inlineStr">
+      <c r="E417" s="4">
+        <v>3</v>
+      </c>
+      <c r="F417" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32952,9 +34206,12 @@
         </is>
       </c>
       <c r="D418" s="4">
+        <v>6</v>
+      </c>
+      <c r="E418" s="4">
         <v>1</v>
       </c>
-      <c r="E418" s="6" t="inlineStr">
+      <c r="F418" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33024,9 +34281,12 @@
         </is>
       </c>
       <c r="D419" s="4">
+        <v>6</v>
+      </c>
+      <c r="E419" s="4">
         <v>2</v>
       </c>
-      <c r="E419" s="6" t="inlineStr">
+      <c r="F419" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33096,9 +34356,12 @@
         </is>
       </c>
       <c r="D420" s="4">
+        <v>6</v>
+      </c>
+      <c r="E420" s="4">
         <v>3</v>
       </c>
-      <c r="E420" s="6" t="inlineStr">
+      <c r="F420" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33168,9 +34431,12 @@
         </is>
       </c>
       <c r="D421" s="4">
+        <v>6</v>
+      </c>
+      <c r="E421" s="4">
         <v>4</v>
       </c>
-      <c r="E421" s="6" t="inlineStr">
+      <c r="F421" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33240,9 +34506,12 @@
         </is>
       </c>
       <c r="D422" s="4">
+        <v>6</v>
+      </c>
+      <c r="E422" s="4">
         <v>5</v>
       </c>
-      <c r="E422" s="6" t="inlineStr">
+      <c r="F422" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33314,7 +34583,10 @@
       <c r="D423" s="4">
         <v>6</v>
       </c>
-      <c r="E423" s="6" t="inlineStr">
+      <c r="E423" s="4">
+        <v>6</v>
+      </c>
+      <c r="F423" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33384,9 +34656,12 @@
         </is>
       </c>
       <c r="D424" s="4">
+        <v>18</v>
+      </c>
+      <c r="E424" s="4">
         <v>1</v>
       </c>
-      <c r="E424" s="6" t="inlineStr">
+      <c r="F424" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33456,9 +34731,12 @@
         </is>
       </c>
       <c r="D425" s="4">
+        <v>18</v>
+      </c>
+      <c r="E425" s="4">
         <v>2</v>
       </c>
-      <c r="E425" s="6" t="inlineStr">
+      <c r="F425" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33519,9 +34797,12 @@
         </is>
       </c>
       <c r="D426" s="4">
+        <v>18</v>
+      </c>
+      <c r="E426" s="4">
         <v>3</v>
       </c>
-      <c r="E426" s="6" t="inlineStr">
+      <c r="F426" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33591,9 +34872,12 @@
         </is>
       </c>
       <c r="D427" s="4">
+        <v>18</v>
+      </c>
+      <c r="E427" s="4">
         <v>4</v>
       </c>
-      <c r="E427" s="6" t="inlineStr">
+      <c r="F427" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33663,9 +34947,12 @@
         </is>
       </c>
       <c r="D428" s="4">
+        <v>18</v>
+      </c>
+      <c r="E428" s="4">
         <v>5</v>
       </c>
-      <c r="E428" s="6" t="inlineStr">
+      <c r="F428" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33726,9 +35013,12 @@
         </is>
       </c>
       <c r="D429" s="4">
+        <v>18</v>
+      </c>
+      <c r="E429" s="4">
         <v>6</v>
       </c>
-      <c r="E429" s="6" t="inlineStr">
+      <c r="F429" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33798,9 +35088,12 @@
         </is>
       </c>
       <c r="D430" s="4">
+        <v>18</v>
+      </c>
+      <c r="E430" s="4">
         <v>7</v>
       </c>
-      <c r="E430" s="6" t="inlineStr">
+      <c r="F430" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33870,9 +35163,12 @@
         </is>
       </c>
       <c r="D431" s="4">
+        <v>18</v>
+      </c>
+      <c r="E431" s="4">
         <v>8</v>
       </c>
-      <c r="E431" s="6" t="inlineStr">
+      <c r="F431" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33942,9 +35238,12 @@
         </is>
       </c>
       <c r="D432" s="4">
+        <v>18</v>
+      </c>
+      <c r="E432" s="4">
         <v>9</v>
       </c>
-      <c r="E432" s="6" t="inlineStr">
+      <c r="F432" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34014,9 +35313,12 @@
         </is>
       </c>
       <c r="D433" s="4">
+        <v>18</v>
+      </c>
+      <c r="E433" s="4">
         <v>10</v>
       </c>
-      <c r="E433" s="6" t="inlineStr">
+      <c r="F433" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34086,9 +35388,12 @@
         </is>
       </c>
       <c r="D434" s="4">
+        <v>18</v>
+      </c>
+      <c r="E434" s="4">
         <v>11</v>
       </c>
-      <c r="E434" s="6" t="inlineStr">
+      <c r="F434" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34158,9 +35463,12 @@
         </is>
       </c>
       <c r="D435" s="4">
+        <v>18</v>
+      </c>
+      <c r="E435" s="4">
         <v>12</v>
       </c>
-      <c r="E435" s="6" t="inlineStr">
+      <c r="F435" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34230,9 +35538,12 @@
         </is>
       </c>
       <c r="D436" s="4">
+        <v>18</v>
+      </c>
+      <c r="E436" s="4">
         <v>13</v>
       </c>
-      <c r="E436" s="6" t="inlineStr">
+      <c r="F436" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34302,9 +35613,12 @@
         </is>
       </c>
       <c r="D437" s="4">
+        <v>18</v>
+      </c>
+      <c r="E437" s="4">
         <v>14</v>
       </c>
-      <c r="E437" s="6" t="inlineStr">
+      <c r="F437" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34374,9 +35688,12 @@
         </is>
       </c>
       <c r="D438" s="4">
+        <v>18</v>
+      </c>
+      <c r="E438" s="4">
         <v>15</v>
       </c>
-      <c r="E438" s="6" t="inlineStr">
+      <c r="F438" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34446,9 +35763,12 @@
         </is>
       </c>
       <c r="D439" s="4">
+        <v>18</v>
+      </c>
+      <c r="E439" s="4">
         <v>16</v>
       </c>
-      <c r="E439" s="6" t="inlineStr">
+      <c r="F439" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34518,9 +35838,12 @@
         </is>
       </c>
       <c r="D440" s="4">
+        <v>18</v>
+      </c>
+      <c r="E440" s="4">
         <v>17</v>
       </c>
-      <c r="E440" s="6" t="inlineStr">
+      <c r="F440" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34592,7 +35915,10 @@
       <c r="D441" s="4">
         <v>18</v>
       </c>
-      <c r="E441" s="6" t="inlineStr">
+      <c r="E441" s="4">
+        <v>18</v>
+      </c>
+      <c r="F441" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34653,9 +35979,12 @@
         </is>
       </c>
       <c r="D442" s="4">
+        <v>2</v>
+      </c>
+      <c r="E442" s="4">
         <v>1</v>
       </c>
-      <c r="E442" s="6" t="inlineStr">
+      <c r="F442" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34711,7 +36040,10 @@
       <c r="D443" s="4">
         <v>2</v>
       </c>
-      <c r="E443" s="6" t="inlineStr">
+      <c r="E443" s="4">
+        <v>2</v>
+      </c>
+      <c r="F443" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34767,7 +36099,10 @@
       <c r="D444" s="4">
         <v>1</v>
       </c>
-      <c r="E444" s="6" t="inlineStr">
+      <c r="E444" s="4">
+        <v>1</v>
+      </c>
+      <c r="F444" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34821,9 +36156,12 @@
         </is>
       </c>
       <c r="D445" s="4">
+        <v>14</v>
+      </c>
+      <c r="E445" s="4">
         <v>1</v>
       </c>
-      <c r="E445" s="6" t="inlineStr">
+      <c r="F445" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34877,9 +36215,12 @@
         </is>
       </c>
       <c r="D446" s="4">
+        <v>14</v>
+      </c>
+      <c r="E446" s="4">
         <v>2</v>
       </c>
-      <c r="E446" s="6" t="inlineStr">
+      <c r="F446" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34933,9 +36274,12 @@
         </is>
       </c>
       <c r="D447" s="4">
+        <v>14</v>
+      </c>
+      <c r="E447" s="4">
         <v>3</v>
       </c>
-      <c r="E447" s="6" t="inlineStr">
+      <c r="F447" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34989,9 +36333,12 @@
         </is>
       </c>
       <c r="D448" s="4">
+        <v>14</v>
+      </c>
+      <c r="E448" s="4">
         <v>4</v>
       </c>
-      <c r="E448" s="6" t="inlineStr">
+      <c r="F448" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35045,9 +36392,12 @@
         </is>
       </c>
       <c r="D449" s="4">
+        <v>14</v>
+      </c>
+      <c r="E449" s="4">
         <v>5</v>
       </c>
-      <c r="E449" s="6" t="inlineStr">
+      <c r="F449" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35101,9 +36451,12 @@
         </is>
       </c>
       <c r="D450" s="4">
+        <v>14</v>
+      </c>
+      <c r="E450" s="4">
         <v>6</v>
       </c>
-      <c r="E450" s="6" t="inlineStr">
+      <c r="F450" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35157,9 +36510,12 @@
         </is>
       </c>
       <c r="D451" s="4">
+        <v>14</v>
+      </c>
+      <c r="E451" s="4">
         <v>7</v>
       </c>
-      <c r="E451" s="6" t="inlineStr">
+      <c r="F451" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35213,9 +36569,12 @@
         </is>
       </c>
       <c r="D452" s="4">
+        <v>14</v>
+      </c>
+      <c r="E452" s="4">
         <v>8</v>
       </c>
-      <c r="E452" s="6" t="inlineStr">
+      <c r="F452" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35269,9 +36628,12 @@
         </is>
       </c>
       <c r="D453" s="4">
+        <v>14</v>
+      </c>
+      <c r="E453" s="4">
         <v>9</v>
       </c>
-      <c r="E453" s="6" t="inlineStr">
+      <c r="F453" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35325,9 +36687,12 @@
         </is>
       </c>
       <c r="D454" s="4">
+        <v>14</v>
+      </c>
+      <c r="E454" s="4">
         <v>10</v>
       </c>
-      <c r="E454" s="6" t="inlineStr">
+      <c r="F454" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35381,9 +36746,12 @@
         </is>
       </c>
       <c r="D455" s="4">
+        <v>14</v>
+      </c>
+      <c r="E455" s="4">
         <v>11</v>
       </c>
-      <c r="E455" s="6" t="inlineStr">
+      <c r="F455" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35437,9 +36805,12 @@
         </is>
       </c>
       <c r="D456" s="4">
+        <v>14</v>
+      </c>
+      <c r="E456" s="4">
         <v>12</v>
       </c>
-      <c r="E456" s="6" t="inlineStr">
+      <c r="F456" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35493,9 +36864,12 @@
         </is>
       </c>
       <c r="D457" s="4">
+        <v>14</v>
+      </c>
+      <c r="E457" s="4">
         <v>13</v>
       </c>
-      <c r="E457" s="6" t="inlineStr">
+      <c r="F457" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35551,7 +36925,10 @@
       <c r="D458" s="4">
         <v>14</v>
       </c>
-      <c r="E458" s="6" t="inlineStr">
+      <c r="E458" s="4">
+        <v>14</v>
+      </c>
+      <c r="F458" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35605,9 +36982,12 @@
         </is>
       </c>
       <c r="D459" s="4">
+        <v>2</v>
+      </c>
+      <c r="E459" s="4">
         <v>1</v>
       </c>
-      <c r="E459" s="6" t="inlineStr">
+      <c r="F459" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35679,7 +37059,10 @@
       <c r="D460" s="4">
         <v>2</v>
       </c>
-      <c r="E460" s="6" t="inlineStr">
+      <c r="E460" s="4">
+        <v>2</v>
+      </c>
+      <c r="F460" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35751,7 +37134,10 @@
       <c r="D461" s="4">
         <v>1</v>
       </c>
-      <c r="E461" s="6" t="inlineStr">
+      <c r="E461" s="4">
+        <v>1</v>
+      </c>
+      <c r="F461" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35812,9 +37198,12 @@
         </is>
       </c>
       <c r="D462" s="4">
+        <v>2</v>
+      </c>
+      <c r="E462" s="4">
         <v>1</v>
       </c>
-      <c r="E462" s="6" t="inlineStr">
+      <c r="F462" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35885,7 +37274,10 @@
       <c r="D463" s="4">
         <v>2</v>
       </c>
-      <c r="E463" s="6" t="inlineStr">
+      <c r="E463" s="4">
+        <v>2</v>
+      </c>
+      <c r="F463" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35954,9 +37346,12 @@
         </is>
       </c>
       <c r="D464" s="4">
+        <v>2</v>
+      </c>
+      <c r="E464" s="4">
         <v>1</v>
       </c>
-      <c r="E464" s="6" t="inlineStr">
+      <c r="F464" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36027,7 +37422,10 @@
       <c r="D465" s="4">
         <v>2</v>
       </c>
-      <c r="E465" s="6" t="inlineStr">
+      <c r="E465" s="4">
+        <v>2</v>
+      </c>
+      <c r="F465" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36113,7 +37511,10 @@
       <c r="D466" s="4">
         <v>1</v>
       </c>
-      <c r="E466" s="6" t="inlineStr">
+      <c r="E466" s="4">
+        <v>1</v>
+      </c>
+      <c r="F466" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36176,7 +37577,10 @@
       <c r="D467" s="4">
         <v>1</v>
       </c>
-      <c r="E467" s="6" t="inlineStr">
+      <c r="E467" s="4">
+        <v>1</v>
+      </c>
+      <c r="F467" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36260,9 +37664,12 @@
         </is>
       </c>
       <c r="D468" s="4">
+        <v>29</v>
+      </c>
+      <c r="E468" s="4">
         <v>1</v>
       </c>
-      <c r="E468" s="6" t="inlineStr">
+      <c r="F468" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36353,9 +37760,12 @@
         </is>
       </c>
       <c r="D469" s="4">
+        <v>29</v>
+      </c>
+      <c r="E469" s="4">
         <v>2</v>
       </c>
-      <c r="E469" s="6" t="inlineStr">
+      <c r="F469" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36506,9 +37916,12 @@
         </is>
       </c>
       <c r="D470" s="4">
+        <v>29</v>
+      </c>
+      <c r="E470" s="4">
         <v>3</v>
       </c>
-      <c r="E470" s="6" t="inlineStr">
+      <c r="F470" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36652,9 +38065,12 @@
         </is>
       </c>
       <c r="D471" s="4">
+        <v>29</v>
+      </c>
+      <c r="E471" s="4">
         <v>4</v>
       </c>
-      <c r="E471" s="6" t="inlineStr">
+      <c r="F471" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36820,9 +38236,12 @@
         </is>
       </c>
       <c r="D472" s="4">
+        <v>29</v>
+      </c>
+      <c r="E472" s="4">
         <v>5</v>
       </c>
-      <c r="E472" s="6" t="inlineStr">
+      <c r="F472" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36958,9 +38377,12 @@
         </is>
       </c>
       <c r="D473" s="4">
+        <v>29</v>
+      </c>
+      <c r="E473" s="4">
         <v>6</v>
       </c>
-      <c r="E473" s="6" t="inlineStr">
+      <c r="F473" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37066,9 +38488,12 @@
         </is>
       </c>
       <c r="D474" s="4">
+        <v>29</v>
+      </c>
+      <c r="E474" s="4">
         <v>7</v>
       </c>
-      <c r="E474" s="6" t="inlineStr">
+      <c r="F474" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37189,9 +38614,12 @@
         </is>
       </c>
       <c r="D475" s="4">
+        <v>29</v>
+      </c>
+      <c r="E475" s="4">
         <v>8</v>
       </c>
-      <c r="E475" s="6" t="inlineStr">
+      <c r="F475" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37282,9 +38710,12 @@
         </is>
       </c>
       <c r="D476" s="4">
+        <v>29</v>
+      </c>
+      <c r="E476" s="4">
         <v>9</v>
       </c>
-      <c r="E476" s="6" t="inlineStr">
+      <c r="F476" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37443,9 +38874,12 @@
         </is>
       </c>
       <c r="D477" s="4">
+        <v>29</v>
+      </c>
+      <c r="E477" s="4">
         <v>10</v>
       </c>
-      <c r="E477" s="6" t="inlineStr">
+      <c r="F477" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37566,9 +39000,12 @@
         </is>
       </c>
       <c r="D478" s="4">
+        <v>29</v>
+      </c>
+      <c r="E478" s="4">
         <v>11</v>
       </c>
-      <c r="E478" s="6" t="inlineStr">
+      <c r="F478" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37719,9 +39156,12 @@
         </is>
       </c>
       <c r="D479" s="4">
+        <v>29</v>
+      </c>
+      <c r="E479" s="4">
         <v>12</v>
       </c>
-      <c r="E479" s="6" t="inlineStr">
+      <c r="F479" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37842,9 +39282,12 @@
         </is>
       </c>
       <c r="D480" s="4">
+        <v>29</v>
+      </c>
+      <c r="E480" s="4">
         <v>13</v>
       </c>
-      <c r="E480" s="6" t="inlineStr">
+      <c r="F480" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37943,9 +39386,12 @@
         </is>
       </c>
       <c r="D481" s="4">
+        <v>29</v>
+      </c>
+      <c r="E481" s="4">
         <v>14</v>
       </c>
-      <c r="E481" s="6" t="inlineStr">
+      <c r="F481" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38066,9 +39512,12 @@
         </is>
       </c>
       <c r="D482" s="4">
+        <v>29</v>
+      </c>
+      <c r="E482" s="4">
         <v>15</v>
       </c>
-      <c r="E482" s="6" t="inlineStr">
+      <c r="F482" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38257,9 +39706,12 @@
         </is>
       </c>
       <c r="D483" s="4">
+        <v>29</v>
+      </c>
+      <c r="E483" s="4">
         <v>16</v>
       </c>
-      <c r="E483" s="6" t="inlineStr">
+      <c r="F483" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38350,9 +39802,12 @@
         </is>
       </c>
       <c r="D484" s="4">
+        <v>29</v>
+      </c>
+      <c r="E484" s="4">
         <v>17</v>
       </c>
-      <c r="E484" s="6" t="inlineStr">
+      <c r="F484" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38496,9 +39951,12 @@
         </is>
       </c>
       <c r="D485" s="4">
+        <v>29</v>
+      </c>
+      <c r="E485" s="4">
         <v>18</v>
       </c>
-      <c r="E485" s="6" t="inlineStr">
+      <c r="F485" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38597,9 +40055,12 @@
         </is>
       </c>
       <c r="D486" s="4">
+        <v>29</v>
+      </c>
+      <c r="E486" s="4">
         <v>19</v>
       </c>
-      <c r="E486" s="6" t="inlineStr">
+      <c r="F486" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38750,9 +40211,12 @@
         </is>
       </c>
       <c r="D487" s="4">
+        <v>29</v>
+      </c>
+      <c r="E487" s="4">
         <v>20</v>
       </c>
-      <c r="E487" s="6" t="inlineStr">
+      <c r="F487" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38845,7 +40309,10 @@
       <c r="D488" s="4">
         <v>1</v>
       </c>
-      <c r="E488" s="6" t="inlineStr">
+      <c r="E488" s="4">
+        <v>1</v>
+      </c>
+      <c r="F488" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38916,7 +40383,10 @@
       <c r="D489" s="4">
         <v>1</v>
       </c>
-      <c r="E489" s="6" t="inlineStr">
+      <c r="E489" s="4">
+        <v>1</v>
+      </c>
+      <c r="F489" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38979,7 +40449,10 @@
       <c r="D490" s="4">
         <v>1</v>
       </c>
-      <c r="E490" s="6" t="inlineStr">
+      <c r="E490" s="4">
+        <v>1</v>
+      </c>
+      <c r="F490" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39093,9 +40566,12 @@
         </is>
       </c>
       <c r="D491" s="4">
+        <v>3</v>
+      </c>
+      <c r="E491" s="4">
         <v>1</v>
       </c>
-      <c r="E491" s="6" t="inlineStr">
+      <c r="F491" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39179,9 +40655,12 @@
         </is>
       </c>
       <c r="D492" s="4">
+        <v>3</v>
+      </c>
+      <c r="E492" s="4">
         <v>2</v>
       </c>
-      <c r="E492" s="6" t="inlineStr">
+      <c r="F492" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39274,7 +40753,10 @@
       <c r="D493" s="4">
         <v>3</v>
       </c>
-      <c r="E493" s="6" t="inlineStr">
+      <c r="E493" s="4">
+        <v>3</v>
+      </c>
+      <c r="F493" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39403,9 +40885,12 @@
         </is>
       </c>
       <c r="D494" s="4">
+        <v>7</v>
+      </c>
+      <c r="E494" s="4">
         <v>1</v>
       </c>
-      <c r="E494" s="6" t="inlineStr">
+      <c r="F494" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39541,9 +41026,12 @@
         </is>
       </c>
       <c r="D495" s="4">
+        <v>7</v>
+      </c>
+      <c r="E495" s="4">
         <v>2</v>
       </c>
-      <c r="E495" s="6" t="inlineStr">
+      <c r="F495" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39679,9 +41167,12 @@
         </is>
       </c>
       <c r="D496" s="4">
+        <v>7</v>
+      </c>
+      <c r="E496" s="4">
         <v>3</v>
       </c>
-      <c r="E496" s="6" t="inlineStr">
+      <c r="F496" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39817,9 +41308,12 @@
         </is>
       </c>
       <c r="D497" s="4">
+        <v>7</v>
+      </c>
+      <c r="E497" s="4">
         <v>4</v>
       </c>
-      <c r="E497" s="6" t="inlineStr">
+      <c r="F497" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39955,9 +41449,12 @@
         </is>
       </c>
       <c r="D498" s="4">
+        <v>7</v>
+      </c>
+      <c r="E498" s="4">
         <v>5</v>
       </c>
-      <c r="E498" s="6" t="inlineStr">
+      <c r="F498" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40138,9 +41635,12 @@
         </is>
       </c>
       <c r="D499" s="4">
+        <v>7</v>
+      </c>
+      <c r="E499" s="4">
         <v>6</v>
       </c>
-      <c r="E499" s="6" t="inlineStr">
+      <c r="F499" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40256,7 +41756,10 @@
       <c r="D500" s="4">
         <v>7</v>
       </c>
-      <c r="E500" s="6" t="inlineStr">
+      <c r="E500" s="4">
+        <v>7</v>
+      </c>
+      <c r="F500" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40409,7 +41912,10 @@
       <c r="D501" s="4">
         <v>1</v>
       </c>
-      <c r="E501" s="6" t="inlineStr">
+      <c r="E501" s="4">
+        <v>1</v>
+      </c>
+      <c r="F501" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40470,9 +41976,12 @@
         </is>
       </c>
       <c r="D502" s="4">
+        <v>2</v>
+      </c>
+      <c r="E502" s="4">
         <v>1</v>
       </c>
-      <c r="E502" s="6" t="inlineStr">
+      <c r="F502" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40535,7 +42044,10 @@
       <c r="D503" s="4">
         <v>2</v>
       </c>
-      <c r="E503" s="6" t="inlineStr">
+      <c r="E503" s="4">
+        <v>2</v>
+      </c>
+      <c r="F503" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40598,7 +42110,10 @@
       <c r="D504" s="4">
         <v>1</v>
       </c>
-      <c r="E504" s="6" t="inlineStr">
+      <c r="E504" s="4">
+        <v>1</v>
+      </c>
+      <c r="F504" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40674,9 +42189,12 @@
         </is>
       </c>
       <c r="D505" s="4">
+        <v>3</v>
+      </c>
+      <c r="E505" s="4">
         <v>1</v>
       </c>
-      <c r="E505" s="6" t="inlineStr">
+      <c r="F505" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40797,9 +42315,12 @@
         </is>
       </c>
       <c r="D506" s="4">
+        <v>3</v>
+      </c>
+      <c r="E506" s="4">
         <v>2</v>
       </c>
-      <c r="E506" s="6" t="inlineStr">
+      <c r="F506" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40877,7 +42398,10 @@
       <c r="D507" s="4">
         <v>3</v>
       </c>
-      <c r="E507" s="6" t="inlineStr">
+      <c r="E507" s="4">
+        <v>3</v>
+      </c>
+      <c r="F507" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40976,9 +42500,12 @@
         </is>
       </c>
       <c r="D508" s="4">
+        <v>2</v>
+      </c>
+      <c r="E508" s="4">
         <v>1</v>
       </c>
-      <c r="E508" s="6" t="inlineStr">
+      <c r="F508" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41050,7 +42577,10 @@
       <c r="D509" s="4">
         <v>2</v>
       </c>
-      <c r="E509" s="6" t="inlineStr">
+      <c r="E509" s="4">
+        <v>2</v>
+      </c>
+      <c r="F509" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41120,9 +42650,12 @@
         </is>
       </c>
       <c r="D510" s="4">
+        <v>7</v>
+      </c>
+      <c r="E510" s="4">
         <v>1</v>
       </c>
-      <c r="E510" s="6" t="inlineStr">
+      <c r="F510" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41192,9 +42725,12 @@
         </is>
       </c>
       <c r="D511" s="4">
+        <v>7</v>
+      </c>
+      <c r="E511" s="4">
         <v>2</v>
       </c>
-      <c r="E511" s="6" t="inlineStr">
+      <c r="F511" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41264,9 +42800,12 @@
         </is>
       </c>
       <c r="D512" s="4">
+        <v>7</v>
+      </c>
+      <c r="E512" s="4">
         <v>3</v>
       </c>
-      <c r="E512" s="6" t="inlineStr">
+      <c r="F512" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41336,9 +42875,12 @@
         </is>
       </c>
       <c r="D513" s="4">
+        <v>7</v>
+      </c>
+      <c r="E513" s="4">
         <v>4</v>
       </c>
-      <c r="E513" s="6" t="inlineStr">
+      <c r="F513" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41408,9 +42950,12 @@
         </is>
       </c>
       <c r="D514" s="4">
+        <v>7</v>
+      </c>
+      <c r="E514" s="4">
         <v>5</v>
       </c>
-      <c r="E514" s="6" t="inlineStr">
+      <c r="F514" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41480,9 +43025,12 @@
         </is>
       </c>
       <c r="D515" s="4">
+        <v>7</v>
+      </c>
+      <c r="E515" s="4">
         <v>6</v>
       </c>
-      <c r="E515" s="6" t="inlineStr">
+      <c r="F515" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41554,7 +43102,10 @@
       <c r="D516" s="4">
         <v>7</v>
       </c>
-      <c r="E516" s="6" t="inlineStr">
+      <c r="E516" s="4">
+        <v>7</v>
+      </c>
+      <c r="F516" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41624,9 +43175,12 @@
         </is>
       </c>
       <c r="D517" s="4">
+        <v>3</v>
+      </c>
+      <c r="E517" s="4">
         <v>1</v>
       </c>
-      <c r="E517" s="6" t="inlineStr">
+      <c r="F517" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41696,9 +43250,12 @@
         </is>
       </c>
       <c r="D518" s="4">
+        <v>3</v>
+      </c>
+      <c r="E518" s="4">
         <v>2</v>
       </c>
-      <c r="E518" s="6" t="inlineStr">
+      <c r="F518" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41770,7 +43327,10 @@
       <c r="D519" s="4">
         <v>3</v>
       </c>
-      <c r="E519" s="6" t="inlineStr">
+      <c r="E519" s="4">
+        <v>3</v>
+      </c>
+      <c r="F519" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41840,9 +43400,12 @@
         </is>
       </c>
       <c r="D520" s="4">
+        <v>4</v>
+      </c>
+      <c r="E520" s="4">
         <v>1</v>
       </c>
-      <c r="E520" s="6" t="inlineStr">
+      <c r="F520" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41912,9 +43475,12 @@
         </is>
       </c>
       <c r="D521" s="4">
+        <v>4</v>
+      </c>
+      <c r="E521" s="4">
         <v>2</v>
       </c>
-      <c r="E521" s="6" t="inlineStr">
+      <c r="F521" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41984,9 +43550,12 @@
         </is>
       </c>
       <c r="D522" s="4">
+        <v>4</v>
+      </c>
+      <c r="E522" s="4">
         <v>3</v>
       </c>
-      <c r="E522" s="6" t="inlineStr">
+      <c r="F522" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42058,7 +43627,10 @@
       <c r="D523" s="4">
         <v>4</v>
       </c>
-      <c r="E523" s="6" t="inlineStr">
+      <c r="E523" s="4">
+        <v>4</v>
+      </c>
+      <c r="F523" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42128,9 +43700,12 @@
         </is>
       </c>
       <c r="D524" s="4">
+        <v>5</v>
+      </c>
+      <c r="E524" s="4">
         <v>1</v>
       </c>
-      <c r="E524" s="6" t="inlineStr">
+      <c r="F524" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42200,9 +43775,12 @@
         </is>
       </c>
       <c r="D525" s="4">
+        <v>5</v>
+      </c>
+      <c r="E525" s="4">
         <v>2</v>
       </c>
-      <c r="E525" s="6" t="inlineStr">
+      <c r="F525" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42272,9 +43850,12 @@
         </is>
       </c>
       <c r="D526" s="4">
+        <v>5</v>
+      </c>
+      <c r="E526" s="4">
         <v>3</v>
       </c>
-      <c r="E526" s="6" t="inlineStr">
+      <c r="F526" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42344,9 +43925,12 @@
         </is>
       </c>
       <c r="D527" s="4">
+        <v>5</v>
+      </c>
+      <c r="E527" s="4">
         <v>4</v>
       </c>
-      <c r="E527" s="6" t="inlineStr">
+      <c r="F527" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42418,7 +44002,10 @@
       <c r="D528" s="4">
         <v>5</v>
       </c>
-      <c r="E528" s="6" t="inlineStr">
+      <c r="E528" s="4">
+        <v>5</v>
+      </c>
+      <c r="F528" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42488,9 +44075,12 @@
         </is>
       </c>
       <c r="D529" s="4">
+        <v>3</v>
+      </c>
+      <c r="E529" s="4">
         <v>1</v>
       </c>
-      <c r="E529" s="6" t="inlineStr">
+      <c r="F529" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42560,9 +44150,12 @@
         </is>
       </c>
       <c r="D530" s="4">
+        <v>3</v>
+      </c>
+      <c r="E530" s="4">
         <v>2</v>
       </c>
-      <c r="E530" s="6" t="inlineStr">
+      <c r="F530" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42634,7 +44227,10 @@
       <c r="D531" s="4">
         <v>3</v>
       </c>
-      <c r="E531" s="6" t="inlineStr">
+      <c r="E531" s="4">
+        <v>3</v>
+      </c>
+      <c r="F531" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42704,9 +44300,12 @@
         </is>
       </c>
       <c r="D532" s="4">
+        <v>6</v>
+      </c>
+      <c r="E532" s="4">
         <v>1</v>
       </c>
-      <c r="E532" s="6" t="inlineStr">
+      <c r="F532" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42776,9 +44375,12 @@
         </is>
       </c>
       <c r="D533" s="4">
+        <v>6</v>
+      </c>
+      <c r="E533" s="4">
         <v>2</v>
       </c>
-      <c r="E533" s="6" t="inlineStr">
+      <c r="F533" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42848,9 +44450,12 @@
         </is>
       </c>
       <c r="D534" s="4">
+        <v>6</v>
+      </c>
+      <c r="E534" s="4">
         <v>3</v>
       </c>
-      <c r="E534" s="6" t="inlineStr">
+      <c r="F534" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42920,9 +44525,12 @@
         </is>
       </c>
       <c r="D535" s="4">
+        <v>6</v>
+      </c>
+      <c r="E535" s="4">
         <v>4</v>
       </c>
-      <c r="E535" s="6" t="inlineStr">
+      <c r="F535" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42992,9 +44600,12 @@
         </is>
       </c>
       <c r="D536" s="4">
+        <v>6</v>
+      </c>
+      <c r="E536" s="4">
         <v>5</v>
       </c>
-      <c r="E536" s="6" t="inlineStr">
+      <c r="F536" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43066,7 +44677,10 @@
       <c r="D537" s="4">
         <v>1</v>
       </c>
-      <c r="E537" s="6" t="inlineStr">
+      <c r="E537" s="4">
+        <v>1</v>
+      </c>
+      <c r="F537" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43136,9 +44750,12 @@
         </is>
       </c>
       <c r="D538" s="4">
+        <v>2</v>
+      </c>
+      <c r="E538" s="4">
         <v>1</v>
       </c>
-      <c r="E538" s="6" t="inlineStr">
+      <c r="F538" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43210,7 +44827,10 @@
       <c r="D539" s="4">
         <v>2</v>
       </c>
-      <c r="E539" s="6" t="inlineStr">
+      <c r="E539" s="4">
+        <v>2</v>
+      </c>
+      <c r="F539" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43280,9 +44900,12 @@
         </is>
       </c>
       <c r="D540" s="4">
+        <v>7</v>
+      </c>
+      <c r="E540" s="4">
         <v>1</v>
       </c>
-      <c r="E540" s="6" t="inlineStr">
+      <c r="F540" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43352,9 +44975,12 @@
         </is>
       </c>
       <c r="D541" s="4">
+        <v>7</v>
+      </c>
+      <c r="E541" s="4">
         <v>2</v>
       </c>
-      <c r="E541" s="6" t="inlineStr">
+      <c r="F541" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43424,9 +45050,12 @@
         </is>
       </c>
       <c r="D542" s="4">
+        <v>7</v>
+      </c>
+      <c r="E542" s="4">
         <v>3</v>
       </c>
-      <c r="E542" s="6" t="inlineStr">
+      <c r="F542" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43496,9 +45125,12 @@
         </is>
       </c>
       <c r="D543" s="4">
+        <v>7</v>
+      </c>
+      <c r="E543" s="4">
         <v>4</v>
       </c>
-      <c r="E543" s="6" t="inlineStr">
+      <c r="F543" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43568,9 +45200,12 @@
         </is>
       </c>
       <c r="D544" s="4">
+        <v>7</v>
+      </c>
+      <c r="E544" s="4">
         <v>5</v>
       </c>
-      <c r="E544" s="6" t="inlineStr">
+      <c r="F544" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43640,9 +45275,12 @@
         </is>
       </c>
       <c r="D545" s="4">
+        <v>7</v>
+      </c>
+      <c r="E545" s="4">
         <v>6</v>
       </c>
-      <c r="E545" s="6" t="inlineStr">
+      <c r="F545" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43714,7 +45352,10 @@
       <c r="D546" s="4">
         <v>7</v>
       </c>
-      <c r="E546" s="6" t="inlineStr">
+      <c r="E546" s="4">
+        <v>7</v>
+      </c>
+      <c r="F546" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43786,7 +45427,10 @@
       <c r="D547" s="4">
         <v>1</v>
       </c>
-      <c r="E547" s="6" t="inlineStr">
+      <c r="E547" s="4">
+        <v>1</v>
+      </c>
+      <c r="F547" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43858,7 +45502,10 @@
       <c r="D548" s="4">
         <v>1</v>
       </c>
-      <c r="E548" s="6" t="inlineStr">
+      <c r="E548" s="4">
+        <v>1</v>
+      </c>
+      <c r="F548" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43928,9 +45575,12 @@
         </is>
       </c>
       <c r="D549" s="4">
+        <v>26</v>
+      </c>
+      <c r="E549" s="4">
         <v>1</v>
       </c>
-      <c r="E549" s="6" t="inlineStr">
+      <c r="F549" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44000,9 +45650,12 @@
         </is>
       </c>
       <c r="D550" s="4">
+        <v>26</v>
+      </c>
+      <c r="E550" s="4">
         <v>2</v>
       </c>
-      <c r="E550" s="6" t="inlineStr">
+      <c r="F550" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44072,9 +45725,12 @@
         </is>
       </c>
       <c r="D551" s="4">
+        <v>26</v>
+      </c>
+      <c r="E551" s="4">
         <v>3</v>
       </c>
-      <c r="E551" s="6" t="inlineStr">
+      <c r="F551" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44144,9 +45800,12 @@
         </is>
       </c>
       <c r="D552" s="4">
+        <v>26</v>
+      </c>
+      <c r="E552" s="4">
         <v>4</v>
       </c>
-      <c r="E552" s="6" t="inlineStr">
+      <c r="F552" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44216,9 +45875,12 @@
         </is>
       </c>
       <c r="D553" s="4">
+        <v>26</v>
+      </c>
+      <c r="E553" s="4">
         <v>5</v>
       </c>
-      <c r="E553" s="6" t="inlineStr">
+      <c r="F553" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44288,9 +45950,12 @@
         </is>
       </c>
       <c r="D554" s="4">
+        <v>26</v>
+      </c>
+      <c r="E554" s="4">
         <v>6</v>
       </c>
-      <c r="E554" s="6" t="inlineStr">
+      <c r="F554" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44360,9 +46025,12 @@
         </is>
       </c>
       <c r="D555" s="4">
+        <v>26</v>
+      </c>
+      <c r="E555" s="4">
         <v>7</v>
       </c>
-      <c r="E555" s="6" t="inlineStr">
+      <c r="F555" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44432,9 +46100,12 @@
         </is>
       </c>
       <c r="D556" s="4">
+        <v>26</v>
+      </c>
+      <c r="E556" s="4">
         <v>8</v>
       </c>
-      <c r="E556" s="6" t="inlineStr">
+      <c r="F556" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44504,9 +46175,12 @@
         </is>
       </c>
       <c r="D557" s="4">
+        <v>26</v>
+      </c>
+      <c r="E557" s="4">
         <v>9</v>
       </c>
-      <c r="E557" s="6" t="inlineStr">
+      <c r="F557" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44576,9 +46250,12 @@
         </is>
       </c>
       <c r="D558" s="4">
+        <v>26</v>
+      </c>
+      <c r="E558" s="4">
         <v>10</v>
       </c>
-      <c r="E558" s="6" t="inlineStr">
+      <c r="F558" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44648,9 +46325,12 @@
         </is>
       </c>
       <c r="D559" s="4">
+        <v>26</v>
+      </c>
+      <c r="E559" s="4">
         <v>11</v>
       </c>
-      <c r="E559" s="6" t="inlineStr">
+      <c r="F559" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44720,9 +46400,12 @@
         </is>
       </c>
       <c r="D560" s="4">
+        <v>26</v>
+      </c>
+      <c r="E560" s="4">
         <v>12</v>
       </c>
-      <c r="E560" s="6" t="inlineStr">
+      <c r="F560" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44792,9 +46475,12 @@
         </is>
       </c>
       <c r="D561" s="4">
+        <v>26</v>
+      </c>
+      <c r="E561" s="4">
         <v>13</v>
       </c>
-      <c r="E561" s="6" t="inlineStr">
+      <c r="F561" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44864,9 +46550,12 @@
         </is>
       </c>
       <c r="D562" s="4">
+        <v>26</v>
+      </c>
+      <c r="E562" s="4">
         <v>14</v>
       </c>
-      <c r="E562" s="6" t="inlineStr">
+      <c r="F562" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44936,9 +46625,12 @@
         </is>
       </c>
       <c r="D563" s="4">
+        <v>26</v>
+      </c>
+      <c r="E563" s="4">
         <v>15</v>
       </c>
-      <c r="E563" s="6" t="inlineStr">
+      <c r="F563" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45008,9 +46700,12 @@
         </is>
       </c>
       <c r="D564" s="4">
+        <v>26</v>
+      </c>
+      <c r="E564" s="4">
         <v>16</v>
       </c>
-      <c r="E564" s="6" t="inlineStr">
+      <c r="F564" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45080,9 +46775,12 @@
         </is>
       </c>
       <c r="D565" s="4">
+        <v>26</v>
+      </c>
+      <c r="E565" s="4">
         <v>17</v>
       </c>
-      <c r="E565" s="6" t="inlineStr">
+      <c r="F565" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45152,9 +46850,12 @@
         </is>
       </c>
       <c r="D566" s="4">
+        <v>26</v>
+      </c>
+      <c r="E566" s="4">
         <v>18</v>
       </c>
-      <c r="E566" s="6" t="inlineStr">
+      <c r="F566" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45224,9 +46925,12 @@
         </is>
       </c>
       <c r="D567" s="4">
+        <v>26</v>
+      </c>
+      <c r="E567" s="4">
         <v>19</v>
       </c>
-      <c r="E567" s="6" t="inlineStr">
+      <c r="F567" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45296,9 +47000,12 @@
         </is>
       </c>
       <c r="D568" s="4">
+        <v>26</v>
+      </c>
+      <c r="E568" s="4">
         <v>20</v>
       </c>
-      <c r="E568" s="6" t="inlineStr">
+      <c r="F568" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45368,9 +47075,12 @@
         </is>
       </c>
       <c r="D569" s="4">
+        <v>14</v>
+      </c>
+      <c r="E569" s="4">
         <v>1</v>
       </c>
-      <c r="E569" s="6" t="inlineStr">
+      <c r="F569" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45440,9 +47150,12 @@
         </is>
       </c>
       <c r="D570" s="4">
+        <v>14</v>
+      </c>
+      <c r="E570" s="4">
         <v>2</v>
       </c>
-      <c r="E570" s="6" t="inlineStr">
+      <c r="F570" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45512,9 +47225,12 @@
         </is>
       </c>
       <c r="D571" s="4">
+        <v>14</v>
+      </c>
+      <c r="E571" s="4">
         <v>3</v>
       </c>
-      <c r="E571" s="6" t="inlineStr">
+      <c r="F571" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45584,9 +47300,12 @@
         </is>
       </c>
       <c r="D572" s="4">
+        <v>14</v>
+      </c>
+      <c r="E572" s="4">
         <v>4</v>
       </c>
-      <c r="E572" s="6" t="inlineStr">
+      <c r="F572" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45656,9 +47375,12 @@
         </is>
       </c>
       <c r="D573" s="4">
+        <v>14</v>
+      </c>
+      <c r="E573" s="4">
         <v>5</v>
       </c>
-      <c r="E573" s="6" t="inlineStr">
+      <c r="F573" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45728,9 +47450,12 @@
         </is>
       </c>
       <c r="D574" s="4">
+        <v>14</v>
+      </c>
+      <c r="E574" s="4">
         <v>6</v>
       </c>
-      <c r="E574" s="6" t="inlineStr">
+      <c r="F574" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45800,9 +47525,12 @@
         </is>
       </c>
       <c r="D575" s="4">
+        <v>14</v>
+      </c>
+      <c r="E575" s="4">
         <v>7</v>
       </c>
-      <c r="E575" s="6" t="inlineStr">
+      <c r="F575" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45872,9 +47600,12 @@
         </is>
       </c>
       <c r="D576" s="4">
+        <v>14</v>
+      </c>
+      <c r="E576" s="4">
         <v>8</v>
       </c>
-      <c r="E576" s="6" t="inlineStr">
+      <c r="F576" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45944,9 +47675,12 @@
         </is>
       </c>
       <c r="D577" s="4">
+        <v>14</v>
+      </c>
+      <c r="E577" s="4">
         <v>9</v>
       </c>
-      <c r="E577" s="6" t="inlineStr">
+      <c r="F577" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46016,9 +47750,12 @@
         </is>
       </c>
       <c r="D578" s="4">
+        <v>14</v>
+      </c>
+      <c r="E578" s="4">
         <v>10</v>
       </c>
-      <c r="E578" s="6" t="inlineStr">
+      <c r="F578" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46088,9 +47825,12 @@
         </is>
       </c>
       <c r="D579" s="4">
+        <v>14</v>
+      </c>
+      <c r="E579" s="4">
         <v>11</v>
       </c>
-      <c r="E579" s="6" t="inlineStr">
+      <c r="F579" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46160,9 +47900,12 @@
         </is>
       </c>
       <c r="D580" s="4">
+        <v>14</v>
+      </c>
+      <c r="E580" s="4">
         <v>12</v>
       </c>
-      <c r="E580" s="6" t="inlineStr">
+      <c r="F580" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46232,9 +47975,12 @@
         </is>
       </c>
       <c r="D581" s="4">
+        <v>14</v>
+      </c>
+      <c r="E581" s="4">
         <v>13</v>
       </c>
-      <c r="E581" s="6" t="inlineStr">
+      <c r="F581" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46304,9 +48050,12 @@
         </is>
       </c>
       <c r="D582" s="4">
+        <v>6</v>
+      </c>
+      <c r="E582" s="4">
         <v>1</v>
       </c>
-      <c r="E582" s="6" t="inlineStr">
+      <c r="F582" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46376,9 +48125,12 @@
         </is>
       </c>
       <c r="D583" s="4">
+        <v>6</v>
+      </c>
+      <c r="E583" s="4">
         <v>2</v>
       </c>
-      <c r="E583" s="6" t="inlineStr">
+      <c r="F583" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46448,9 +48200,12 @@
         </is>
       </c>
       <c r="D584" s="4">
+        <v>6</v>
+      </c>
+      <c r="E584" s="4">
         <v>3</v>
       </c>
-      <c r="E584" s="6" t="inlineStr">
+      <c r="F584" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46520,9 +48275,12 @@
         </is>
       </c>
       <c r="D585" s="4">
+        <v>6</v>
+      </c>
+      <c r="E585" s="4">
         <v>4</v>
       </c>
-      <c r="E585" s="6" t="inlineStr">
+      <c r="F585" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46592,9 +48350,12 @@
         </is>
       </c>
       <c r="D586" s="4">
+        <v>6</v>
+      </c>
+      <c r="E586" s="4">
         <v>5</v>
       </c>
-      <c r="E586" s="6" t="inlineStr">
+      <c r="F586" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46666,7 +48427,10 @@
       <c r="D587" s="4">
         <v>6</v>
       </c>
-      <c r="E587" s="6" t="inlineStr">
+      <c r="E587" s="4">
+        <v>6</v>
+      </c>
+      <c r="F587" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46736,9 +48500,12 @@
         </is>
       </c>
       <c r="D588" s="4">
+        <v>2</v>
+      </c>
+      <c r="E588" s="4">
         <v>1</v>
       </c>
-      <c r="E588" s="6" t="inlineStr">
+      <c r="F588" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46810,7 +48577,10 @@
       <c r="D589" s="4">
         <v>2</v>
       </c>
-      <c r="E589" s="6" t="inlineStr">
+      <c r="E589" s="4">
+        <v>2</v>
+      </c>
+      <c r="F589" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46880,9 +48650,12 @@
         </is>
       </c>
       <c r="D590" s="4">
+        <v>3</v>
+      </c>
+      <c r="E590" s="4">
         <v>1</v>
       </c>
-      <c r="E590" s="6" t="inlineStr">
+      <c r="F590" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46952,9 +48725,12 @@
         </is>
       </c>
       <c r="D591" s="4">
+        <v>3</v>
+      </c>
+      <c r="E591" s="4">
         <v>2</v>
       </c>
-      <c r="E591" s="6" t="inlineStr">
+      <c r="F591" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47026,7 +48802,10 @@
       <c r="D592" s="4">
         <v>3</v>
       </c>
-      <c r="E592" s="6" t="inlineStr">
+      <c r="E592" s="4">
+        <v>3</v>
+      </c>
+      <c r="F592" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47096,9 +48875,12 @@
         </is>
       </c>
       <c r="D593" s="4">
+        <v>4</v>
+      </c>
+      <c r="E593" s="4">
         <v>1</v>
       </c>
-      <c r="E593" s="6" t="inlineStr">
+      <c r="F593" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47168,9 +48950,12 @@
         </is>
       </c>
       <c r="D594" s="4">
+        <v>4</v>
+      </c>
+      <c r="E594" s="4">
         <v>2</v>
       </c>
-      <c r="E594" s="6" t="inlineStr">
+      <c r="F594" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47240,9 +49025,12 @@
         </is>
       </c>
       <c r="D595" s="4">
+        <v>4</v>
+      </c>
+      <c r="E595" s="4">
         <v>3</v>
       </c>
-      <c r="E595" s="6" t="inlineStr">
+      <c r="F595" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47314,7 +49102,10 @@
       <c r="D596" s="4">
         <v>4</v>
       </c>
-      <c r="E596" s="6" t="inlineStr">
+      <c r="E596" s="4">
+        <v>4</v>
+      </c>
+      <c r="F596" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47368,322 +49159,427 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="315">
+  <mergeCells count="420">
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="B21:B25"/>
     <mergeCell ref="C21:C25"/>
+    <mergeCell ref="D21:D25"/>
     <mergeCell ref="A26:A30"/>
     <mergeCell ref="B26:B30"/>
     <mergeCell ref="C26:C30"/>
+    <mergeCell ref="D26:D30"/>
     <mergeCell ref="A31:A35"/>
     <mergeCell ref="B31:B35"/>
     <mergeCell ref="C31:C35"/>
+    <mergeCell ref="D31:D35"/>
     <mergeCell ref="A36:A40"/>
     <mergeCell ref="B36:B40"/>
     <mergeCell ref="C36:C40"/>
+    <mergeCell ref="D36:D40"/>
     <mergeCell ref="A41:A45"/>
     <mergeCell ref="B41:B45"/>
     <mergeCell ref="C41:C45"/>
+    <mergeCell ref="D41:D45"/>
     <mergeCell ref="A46:A50"/>
     <mergeCell ref="B46:B50"/>
     <mergeCell ref="C46:C50"/>
+    <mergeCell ref="D46:D50"/>
     <mergeCell ref="A51:A55"/>
     <mergeCell ref="B51:B55"/>
     <mergeCell ref="C51:C55"/>
+    <mergeCell ref="D51:D55"/>
     <mergeCell ref="A56:A60"/>
     <mergeCell ref="B56:B60"/>
     <mergeCell ref="C56:C60"/>
+    <mergeCell ref="D56:D60"/>
     <mergeCell ref="A61:A65"/>
     <mergeCell ref="B61:B65"/>
     <mergeCell ref="C61:C65"/>
+    <mergeCell ref="D61:D65"/>
     <mergeCell ref="A66:A70"/>
     <mergeCell ref="B66:B70"/>
     <mergeCell ref="C66:C70"/>
+    <mergeCell ref="D66:D70"/>
     <mergeCell ref="A71:A75"/>
     <mergeCell ref="B71:B75"/>
     <mergeCell ref="C71:C75"/>
+    <mergeCell ref="D71:D75"/>
     <mergeCell ref="A76:A80"/>
     <mergeCell ref="B76:B80"/>
     <mergeCell ref="C76:C80"/>
+    <mergeCell ref="D76:D80"/>
     <mergeCell ref="A81:A85"/>
     <mergeCell ref="B81:B85"/>
     <mergeCell ref="C81:C85"/>
+    <mergeCell ref="D81:D85"/>
     <mergeCell ref="A86:A90"/>
     <mergeCell ref="B86:B90"/>
     <mergeCell ref="C86:C90"/>
+    <mergeCell ref="D86:D90"/>
     <mergeCell ref="A91:A95"/>
     <mergeCell ref="B91:B95"/>
     <mergeCell ref="C91:C95"/>
+    <mergeCell ref="D91:D95"/>
     <mergeCell ref="A96:A100"/>
     <mergeCell ref="B96:B100"/>
     <mergeCell ref="C96:C100"/>
+    <mergeCell ref="D96:D100"/>
     <mergeCell ref="A101:A105"/>
     <mergeCell ref="B101:B105"/>
     <mergeCell ref="C101:C105"/>
+    <mergeCell ref="D101:D105"/>
     <mergeCell ref="A106:A110"/>
     <mergeCell ref="B106:B110"/>
     <mergeCell ref="C106:C110"/>
+    <mergeCell ref="D106:D110"/>
     <mergeCell ref="A111:A113"/>
     <mergeCell ref="B111:B113"/>
     <mergeCell ref="C111:C113"/>
+    <mergeCell ref="D111:D113"/>
     <mergeCell ref="A114:A118"/>
     <mergeCell ref="B114:B118"/>
     <mergeCell ref="C114:C118"/>
+    <mergeCell ref="D114:D118"/>
     <mergeCell ref="A119:A123"/>
     <mergeCell ref="B119:B123"/>
     <mergeCell ref="C119:C123"/>
+    <mergeCell ref="D119:D123"/>
     <mergeCell ref="A127:A128"/>
     <mergeCell ref="B127:B128"/>
     <mergeCell ref="C127:C128"/>
+    <mergeCell ref="D127:D128"/>
     <mergeCell ref="A139:A140"/>
     <mergeCell ref="B139:B140"/>
     <mergeCell ref="C139:C140"/>
+    <mergeCell ref="D139:D140"/>
     <mergeCell ref="A149:A150"/>
     <mergeCell ref="B149:B150"/>
     <mergeCell ref="C149:C150"/>
+    <mergeCell ref="D149:D150"/>
     <mergeCell ref="A151:A153"/>
     <mergeCell ref="B151:B153"/>
     <mergeCell ref="C151:C153"/>
+    <mergeCell ref="D151:D153"/>
     <mergeCell ref="A157:A158"/>
     <mergeCell ref="B157:B158"/>
     <mergeCell ref="C157:C158"/>
+    <mergeCell ref="D157:D158"/>
     <mergeCell ref="A168:A169"/>
     <mergeCell ref="B168:B169"/>
     <mergeCell ref="C168:C169"/>
+    <mergeCell ref="D168:D169"/>
     <mergeCell ref="A170:A172"/>
     <mergeCell ref="B170:B172"/>
     <mergeCell ref="C170:C172"/>
+    <mergeCell ref="D170:D172"/>
     <mergeCell ref="A185:A186"/>
     <mergeCell ref="B185:B186"/>
     <mergeCell ref="C185:C186"/>
+    <mergeCell ref="D185:D186"/>
     <mergeCell ref="A188:A189"/>
     <mergeCell ref="B188:B189"/>
     <mergeCell ref="C188:C189"/>
+    <mergeCell ref="D188:D189"/>
     <mergeCell ref="A192:A194"/>
     <mergeCell ref="B192:B194"/>
     <mergeCell ref="C192:C194"/>
+    <mergeCell ref="D192:D194"/>
     <mergeCell ref="A195:A199"/>
     <mergeCell ref="B195:B199"/>
     <mergeCell ref="C195:C199"/>
+    <mergeCell ref="D195:D199"/>
     <mergeCell ref="A204:A205"/>
     <mergeCell ref="B204:B205"/>
     <mergeCell ref="C204:C205"/>
+    <mergeCell ref="D204:D205"/>
     <mergeCell ref="A206:A208"/>
     <mergeCell ref="B206:B208"/>
     <mergeCell ref="C206:C208"/>
+    <mergeCell ref="D206:D208"/>
     <mergeCell ref="A209:A213"/>
     <mergeCell ref="B209:B213"/>
     <mergeCell ref="C209:C213"/>
+    <mergeCell ref="D209:D213"/>
     <mergeCell ref="A214:A218"/>
     <mergeCell ref="B214:B218"/>
     <mergeCell ref="C214:C218"/>
+    <mergeCell ref="D214:D218"/>
     <mergeCell ref="A219:A221"/>
     <mergeCell ref="B219:B221"/>
     <mergeCell ref="C219:C221"/>
+    <mergeCell ref="D219:D221"/>
     <mergeCell ref="A222:A226"/>
     <mergeCell ref="B222:B226"/>
     <mergeCell ref="C222:C226"/>
+    <mergeCell ref="D222:D226"/>
     <mergeCell ref="A233:A234"/>
     <mergeCell ref="B233:B234"/>
     <mergeCell ref="C233:C234"/>
+    <mergeCell ref="D233:D234"/>
     <mergeCell ref="A238:A240"/>
     <mergeCell ref="B238:B240"/>
     <mergeCell ref="C238:C240"/>
+    <mergeCell ref="D238:D240"/>
     <mergeCell ref="A241:A242"/>
     <mergeCell ref="B241:B242"/>
     <mergeCell ref="C241:C242"/>
+    <mergeCell ref="D241:D242"/>
     <mergeCell ref="A243:A244"/>
     <mergeCell ref="B243:B244"/>
     <mergeCell ref="C243:C244"/>
+    <mergeCell ref="D243:D244"/>
     <mergeCell ref="A245:A246"/>
     <mergeCell ref="B245:B246"/>
     <mergeCell ref="C245:C246"/>
+    <mergeCell ref="D245:D246"/>
     <mergeCell ref="A247:A249"/>
     <mergeCell ref="B247:B249"/>
     <mergeCell ref="C247:C249"/>
+    <mergeCell ref="D247:D249"/>
     <mergeCell ref="A253:A256"/>
     <mergeCell ref="B253:B256"/>
     <mergeCell ref="C253:C256"/>
+    <mergeCell ref="D253:D256"/>
     <mergeCell ref="A257:A259"/>
     <mergeCell ref="B257:B259"/>
     <mergeCell ref="C257:C259"/>
+    <mergeCell ref="D257:D259"/>
     <mergeCell ref="A264:A267"/>
     <mergeCell ref="B264:B267"/>
     <mergeCell ref="C264:C267"/>
+    <mergeCell ref="D264:D267"/>
     <mergeCell ref="A268:A270"/>
     <mergeCell ref="B268:B270"/>
     <mergeCell ref="C268:C270"/>
+    <mergeCell ref="D268:D270"/>
     <mergeCell ref="A271:A275"/>
     <mergeCell ref="B271:B275"/>
     <mergeCell ref="C271:C275"/>
+    <mergeCell ref="D271:D275"/>
     <mergeCell ref="A277:A281"/>
     <mergeCell ref="B277:B281"/>
     <mergeCell ref="C277:C281"/>
+    <mergeCell ref="D277:D281"/>
     <mergeCell ref="A282:A284"/>
     <mergeCell ref="B282:B284"/>
     <mergeCell ref="C282:C284"/>
+    <mergeCell ref="D282:D284"/>
     <mergeCell ref="A285:A287"/>
     <mergeCell ref="B285:B287"/>
     <mergeCell ref="C285:C287"/>
+    <mergeCell ref="D285:D287"/>
     <mergeCell ref="A288:A290"/>
     <mergeCell ref="B288:B290"/>
     <mergeCell ref="C288:C290"/>
+    <mergeCell ref="D288:D290"/>
     <mergeCell ref="A292:A293"/>
     <mergeCell ref="B292:B293"/>
     <mergeCell ref="C292:C293"/>
+    <mergeCell ref="D292:D293"/>
     <mergeCell ref="A295:A300"/>
     <mergeCell ref="B295:B300"/>
     <mergeCell ref="C295:C300"/>
+    <mergeCell ref="D295:D300"/>
     <mergeCell ref="A301:A304"/>
     <mergeCell ref="B301:B304"/>
     <mergeCell ref="C301:C304"/>
+    <mergeCell ref="D301:D304"/>
     <mergeCell ref="A305:A306"/>
     <mergeCell ref="B305:B306"/>
     <mergeCell ref="C305:C306"/>
+    <mergeCell ref="D305:D306"/>
     <mergeCell ref="A307:A309"/>
     <mergeCell ref="B307:B309"/>
     <mergeCell ref="C307:C309"/>
+    <mergeCell ref="D307:D309"/>
     <mergeCell ref="A311:A315"/>
     <mergeCell ref="B311:B315"/>
     <mergeCell ref="C311:C315"/>
+    <mergeCell ref="D311:D315"/>
     <mergeCell ref="A316:A318"/>
     <mergeCell ref="B316:B318"/>
     <mergeCell ref="C316:C318"/>
+    <mergeCell ref="D316:D318"/>
     <mergeCell ref="A319:A320"/>
     <mergeCell ref="B319:B320"/>
     <mergeCell ref="C319:C320"/>
+    <mergeCell ref="D319:D320"/>
     <mergeCell ref="A322:A329"/>
     <mergeCell ref="B322:B329"/>
     <mergeCell ref="C322:C329"/>
+    <mergeCell ref="D322:D329"/>
     <mergeCell ref="A330:A333"/>
     <mergeCell ref="B330:B333"/>
     <mergeCell ref="C330:C333"/>
+    <mergeCell ref="D330:D333"/>
     <mergeCell ref="A334:A347"/>
     <mergeCell ref="B334:B347"/>
     <mergeCell ref="C334:C347"/>
+    <mergeCell ref="D334:D347"/>
     <mergeCell ref="A348:A356"/>
     <mergeCell ref="B348:B356"/>
     <mergeCell ref="C348:C356"/>
+    <mergeCell ref="D348:D356"/>
     <mergeCell ref="A357:A358"/>
     <mergeCell ref="B357:B358"/>
     <mergeCell ref="C357:C358"/>
+    <mergeCell ref="D357:D358"/>
     <mergeCell ref="A361:A380"/>
     <mergeCell ref="B361:B380"/>
     <mergeCell ref="C361:C380"/>
+    <mergeCell ref="D361:D380"/>
     <mergeCell ref="A382:A385"/>
     <mergeCell ref="B382:B385"/>
     <mergeCell ref="C382:C385"/>
+    <mergeCell ref="D382:D385"/>
     <mergeCell ref="A386:A388"/>
     <mergeCell ref="B386:B388"/>
     <mergeCell ref="C386:C388"/>
+    <mergeCell ref="D386:D388"/>
     <mergeCell ref="A389:A390"/>
     <mergeCell ref="B389:B390"/>
     <mergeCell ref="C389:C390"/>
+    <mergeCell ref="D389:D390"/>
     <mergeCell ref="A391:A395"/>
     <mergeCell ref="B391:B395"/>
     <mergeCell ref="C391:C395"/>
+    <mergeCell ref="D391:D395"/>
     <mergeCell ref="A397:A400"/>
     <mergeCell ref="B397:B400"/>
     <mergeCell ref="C397:C400"/>
+    <mergeCell ref="D397:D400"/>
     <mergeCell ref="A402:A403"/>
     <mergeCell ref="B402:B403"/>
     <mergeCell ref="C402:C403"/>
+    <mergeCell ref="D402:D403"/>
     <mergeCell ref="A405:A406"/>
     <mergeCell ref="B405:B406"/>
     <mergeCell ref="C405:C406"/>
+    <mergeCell ref="D405:D406"/>
     <mergeCell ref="A407:A409"/>
     <mergeCell ref="B407:B409"/>
     <mergeCell ref="C407:C409"/>
+    <mergeCell ref="D407:D409"/>
     <mergeCell ref="A410:A414"/>
     <mergeCell ref="B410:B414"/>
     <mergeCell ref="C410:C414"/>
+    <mergeCell ref="D410:D414"/>
     <mergeCell ref="A415:A417"/>
     <mergeCell ref="B415:B417"/>
     <mergeCell ref="C415:C417"/>
+    <mergeCell ref="D415:D417"/>
     <mergeCell ref="A418:A423"/>
     <mergeCell ref="B418:B423"/>
     <mergeCell ref="C418:C423"/>
+    <mergeCell ref="D418:D423"/>
     <mergeCell ref="A424:A441"/>
     <mergeCell ref="B424:B441"/>
     <mergeCell ref="C424:C441"/>
+    <mergeCell ref="D424:D441"/>
     <mergeCell ref="A442:A443"/>
     <mergeCell ref="B442:B443"/>
     <mergeCell ref="C442:C443"/>
+    <mergeCell ref="D442:D443"/>
     <mergeCell ref="A445:A458"/>
     <mergeCell ref="B445:B458"/>
     <mergeCell ref="C445:C458"/>
+    <mergeCell ref="D445:D458"/>
     <mergeCell ref="A459:A460"/>
     <mergeCell ref="B459:B460"/>
     <mergeCell ref="C459:C460"/>
+    <mergeCell ref="D459:D460"/>
     <mergeCell ref="A462:A463"/>
     <mergeCell ref="B462:B463"/>
     <mergeCell ref="C462:C463"/>
+    <mergeCell ref="D462:D463"/>
     <mergeCell ref="A464:A465"/>
     <mergeCell ref="B464:B465"/>
     <mergeCell ref="C464:C465"/>
+    <mergeCell ref="D464:D465"/>
     <mergeCell ref="A468:A487"/>
     <mergeCell ref="B468:B487"/>
     <mergeCell ref="C468:C487"/>
+    <mergeCell ref="D468:D487"/>
     <mergeCell ref="A491:A493"/>
     <mergeCell ref="B491:B493"/>
     <mergeCell ref="C491:C493"/>
+    <mergeCell ref="D491:D493"/>
     <mergeCell ref="A494:A500"/>
     <mergeCell ref="B494:B500"/>
     <mergeCell ref="C494:C500"/>
+    <mergeCell ref="D494:D500"/>
     <mergeCell ref="A502:A503"/>
     <mergeCell ref="B502:B503"/>
     <mergeCell ref="C502:C503"/>
+    <mergeCell ref="D502:D503"/>
     <mergeCell ref="A505:A507"/>
     <mergeCell ref="B505:B507"/>
     <mergeCell ref="C505:C507"/>
+    <mergeCell ref="D505:D507"/>
     <mergeCell ref="A508:A509"/>
     <mergeCell ref="B508:B509"/>
     <mergeCell ref="C508:C509"/>
+    <mergeCell ref="D508:D509"/>
     <mergeCell ref="A510:A516"/>
     <mergeCell ref="B510:B516"/>
     <mergeCell ref="C510:C516"/>
+    <mergeCell ref="D510:D516"/>
     <mergeCell ref="A517:A519"/>
     <mergeCell ref="B517:B519"/>
     <mergeCell ref="C517:C519"/>
+    <mergeCell ref="D517:D519"/>
     <mergeCell ref="A520:A523"/>
     <mergeCell ref="B520:B523"/>
     <mergeCell ref="C520:C523"/>
+    <mergeCell ref="D520:D523"/>
     <mergeCell ref="A524:A528"/>
     <mergeCell ref="B524:B528"/>
     <mergeCell ref="C524:C528"/>
+    <mergeCell ref="D524:D528"/>
     <mergeCell ref="A529:A531"/>
     <mergeCell ref="B529:B531"/>
     <mergeCell ref="C529:C531"/>
+    <mergeCell ref="D529:D531"/>
     <mergeCell ref="A532:A536"/>
     <mergeCell ref="B532:B536"/>
     <mergeCell ref="C532:C536"/>
+    <mergeCell ref="D532:D536"/>
     <mergeCell ref="A538:A539"/>
     <mergeCell ref="B538:B539"/>
     <mergeCell ref="C538:C539"/>
+    <mergeCell ref="D538:D539"/>
     <mergeCell ref="A540:A546"/>
     <mergeCell ref="B540:B546"/>
     <mergeCell ref="C540:C546"/>
+    <mergeCell ref="D540:D546"/>
     <mergeCell ref="A549:A568"/>
     <mergeCell ref="B549:B568"/>
     <mergeCell ref="C549:C568"/>
+    <mergeCell ref="D549:D568"/>
     <mergeCell ref="A569:A581"/>
     <mergeCell ref="B569:B581"/>
     <mergeCell ref="C569:C581"/>
+    <mergeCell ref="D569:D581"/>
     <mergeCell ref="A582:A587"/>
     <mergeCell ref="B582:B587"/>
     <mergeCell ref="C582:C587"/>
+    <mergeCell ref="D582:D587"/>
     <mergeCell ref="A588:A589"/>
     <mergeCell ref="B588:B589"/>
     <mergeCell ref="C588:C589"/>
+    <mergeCell ref="D588:D589"/>
     <mergeCell ref="A590:A592"/>
     <mergeCell ref="B590:B592"/>
     <mergeCell ref="C590:C592"/>
+    <mergeCell ref="D590:D592"/>
     <mergeCell ref="A593:A596"/>
     <mergeCell ref="B593:B596"/>
     <mergeCell ref="C593:C596"/>
+    <mergeCell ref="D593:D596"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
